--- a/docs/template_funcionarios.xlsx
+++ b/docs/template_funcionarios.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,6 +71,11 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="001e293b"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <color rgb="00475569"/>
       <sz val="10"/>
     </font>
@@ -85,7 +90,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -109,12 +114,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE0E0"/>
+        <fgColor rgb="00FFD6D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDF1F7"/>
+        <fgColor rgb="00E8F4FD"/>
       </patternFill>
     </fill>
     <fill>
@@ -125,6 +130,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDF1F7"/>
       </patternFill>
     </fill>
     <fill>
@@ -192,7 +202,7 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -201,29 +211,29 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -594,13 +604,13 @@
   <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28.57142857142857" customWidth="1" min="1" max="1"/>
-    <col width="31.42857142857143" customWidth="1" min="2" max="2"/>
-    <col width="18.57142857142857" customWidth="1" min="3" max="3"/>
-    <col width="25.71428571428572" customWidth="1" min="4" max="4"/>
-    <col width="18.57142857142857" customWidth="1" min="5" max="5"/>
-    <col width="17.14285714285714" customWidth="1" min="6" max="6"/>
-    <col width="15.71428571428571" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -613,11 +623,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>🔴 Campo obrigatório (fundo rosa)   |   ⚪ Campo opcional (fundo azul)   |   🟢 Linha de exemplo (não importar)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+          <t>🔴 Campo obrigatório (fundo rosa)   |   🔵 Campo opcional (fundo azul)   |   🟢 Linha de exemplo (não importar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Nome Completo *</t>
@@ -635,22 +645,22 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Cargo / Função</t>
+          <t>Cargo / Função *</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Custo por Hora (R$)</t>
+          <t>Custo por Hora (R$) *</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Horas por Dia Útil</t>
+          <t>Horas por Dia Útil *</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Ativo (SIM/NÃO)</t>
+          <t>Ativo (SIM/NÃO) *</t>
         </is>
       </c>
     </row>
@@ -687,1118 +697,1521 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="18" customHeight="1">
       <c r="A5" s="6" t="n"/>
       <c r="B5" s="7" t="n"/>
       <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
+      <c r="D5" s="6" t="n"/>
       <c r="E5" s="8" t="n"/>
-      <c r="F5" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G5" s="7" t="n"/>
-    </row>
-    <row r="6">
+      <c r="F5" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
       <c r="A6" s="6" t="n"/>
       <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
+      <c r="D6" s="6" t="n"/>
       <c r="E6" s="8" t="n"/>
-      <c r="F6" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G6" s="7" t="n"/>
-    </row>
-    <row r="7">
+      <c r="F6" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="n"/>
       <c r="B7" s="7" t="n"/>
       <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
+      <c r="D7" s="6" t="n"/>
       <c r="E7" s="8" t="n"/>
-      <c r="F7" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G7" s="7" t="n"/>
-    </row>
-    <row r="8">
+      <c r="F7" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
       <c r="A8" s="6" t="n"/>
       <c r="B8" s="7" t="n"/>
       <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
+      <c r="D8" s="6" t="n"/>
       <c r="E8" s="8" t="n"/>
-      <c r="F8" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G8" s="7" t="n"/>
-    </row>
-    <row r="9">
+      <c r="F8" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n"/>
       <c r="B9" s="7" t="n"/>
       <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
+      <c r="D9" s="6" t="n"/>
       <c r="E9" s="8" t="n"/>
-      <c r="F9" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G9" s="7" t="n"/>
-    </row>
-    <row r="10">
+      <c r="F9" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
       <c r="A10" s="6" t="n"/>
       <c r="B10" s="7" t="n"/>
       <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
+      <c r="D10" s="6" t="n"/>
       <c r="E10" s="8" t="n"/>
-      <c r="F10" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G10" s="7" t="n"/>
-    </row>
-    <row r="11">
+      <c r="F10" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="n"/>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
+      <c r="D11" s="6" t="n"/>
       <c r="E11" s="8" t="n"/>
-      <c r="F11" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G11" s="7" t="n"/>
-    </row>
-    <row r="12">
+      <c r="F11" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
       <c r="A12" s="6" t="n"/>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
+      <c r="D12" s="6" t="n"/>
       <c r="E12" s="8" t="n"/>
-      <c r="F12" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G12" s="7" t="n"/>
-    </row>
-    <row r="13">
+      <c r="F12" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n"/>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
+      <c r="D13" s="6" t="n"/>
       <c r="E13" s="8" t="n"/>
-      <c r="F13" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G13" s="7" t="n"/>
-    </row>
-    <row r="14">
+      <c r="F13" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
       <c r="A14" s="6" t="n"/>
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
+      <c r="D14" s="6" t="n"/>
       <c r="E14" s="8" t="n"/>
-      <c r="F14" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G14" s="7" t="n"/>
-    </row>
-    <row r="15">
+      <c r="F14" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="n"/>
       <c r="B15" s="7" t="n"/>
       <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
+      <c r="D15" s="6" t="n"/>
       <c r="E15" s="8" t="n"/>
-      <c r="F15" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G15" s="7" t="n"/>
-    </row>
-    <row r="16">
+      <c r="F15" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
       <c r="A16" s="6" t="n"/>
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
+      <c r="D16" s="6" t="n"/>
       <c r="E16" s="8" t="n"/>
-      <c r="F16" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G16" s="7" t="n"/>
-    </row>
-    <row r="17">
+      <c r="F16" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n"/>
       <c r="B17" s="7" t="n"/>
       <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
+      <c r="D17" s="6" t="n"/>
       <c r="E17" s="8" t="n"/>
-      <c r="F17" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G17" s="7" t="n"/>
-    </row>
-    <row r="18">
+      <c r="F17" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
       <c r="A18" s="6" t="n"/>
       <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
+      <c r="D18" s="6" t="n"/>
       <c r="E18" s="8" t="n"/>
-      <c r="F18" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G18" s="7" t="n"/>
-    </row>
-    <row r="19">
+      <c r="F18" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="n"/>
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
+      <c r="D19" s="6" t="n"/>
       <c r="E19" s="8" t="n"/>
-      <c r="F19" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G19" s="7" t="n"/>
-    </row>
-    <row r="20">
+      <c r="F19" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
       <c r="A20" s="6" t="n"/>
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
+      <c r="D20" s="6" t="n"/>
       <c r="E20" s="8" t="n"/>
-      <c r="F20" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G20" s="7" t="n"/>
-    </row>
-    <row r="21">
+      <c r="F20" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="n"/>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
+      <c r="D21" s="6" t="n"/>
       <c r="E21" s="8" t="n"/>
-      <c r="F21" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G21" s="7" t="n"/>
-    </row>
-    <row r="22">
+      <c r="F21" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
       <c r="A22" s="6" t="n"/>
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
+      <c r="D22" s="6" t="n"/>
       <c r="E22" s="8" t="n"/>
-      <c r="F22" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G22" s="7" t="n"/>
-    </row>
-    <row r="23">
+      <c r="F22" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="n"/>
       <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
+      <c r="D23" s="6" t="n"/>
       <c r="E23" s="8" t="n"/>
-      <c r="F23" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G23" s="7" t="n"/>
-    </row>
-    <row r="24">
+      <c r="F23" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
       <c r="A24" s="6" t="n"/>
       <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
+      <c r="D24" s="6" t="n"/>
       <c r="E24" s="8" t="n"/>
-      <c r="F24" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G24" s="7" t="n"/>
-    </row>
-    <row r="25">
+      <c r="F24" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
       <c r="A25" s="6" t="n"/>
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
+      <c r="D25" s="6" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G25" s="7" t="n"/>
-    </row>
-    <row r="26">
+      <c r="F25" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
       <c r="A26" s="6" t="n"/>
       <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
+      <c r="D26" s="6" t="n"/>
       <c r="E26" s="8" t="n"/>
-      <c r="F26" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G26" s="7" t="n"/>
-    </row>
-    <row r="27">
+      <c r="F26" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
       <c r="A27" s="6" t="n"/>
       <c r="B27" s="7" t="n"/>
       <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
+      <c r="D27" s="6" t="n"/>
       <c r="E27" s="8" t="n"/>
-      <c r="F27" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G27" s="7" t="n"/>
-    </row>
-    <row r="28">
+      <c r="F27" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
       <c r="A28" s="6" t="n"/>
       <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
+      <c r="D28" s="6" t="n"/>
       <c r="E28" s="8" t="n"/>
-      <c r="F28" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G28" s="7" t="n"/>
-    </row>
-    <row r="29">
+      <c r="F28" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
       <c r="A29" s="6" t="n"/>
       <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="n"/>
+      <c r="D29" s="6" t="n"/>
       <c r="E29" s="8" t="n"/>
-      <c r="F29" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G29" s="7" t="n"/>
-    </row>
-    <row r="30">
+      <c r="F29" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
       <c r="A30" s="6" t="n"/>
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
-      <c r="D30" s="7" t="n"/>
+      <c r="D30" s="6" t="n"/>
       <c r="E30" s="8" t="n"/>
-      <c r="F30" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G30" s="7" t="n"/>
-    </row>
-    <row r="31">
+      <c r="F30" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
       <c r="A31" s="6" t="n"/>
       <c r="B31" s="7" t="n"/>
       <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="n"/>
+      <c r="D31" s="6" t="n"/>
       <c r="E31" s="8" t="n"/>
-      <c r="F31" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G31" s="7" t="n"/>
-    </row>
-    <row r="32">
+      <c r="F31" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
       <c r="A32" s="6" t="n"/>
       <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
+      <c r="D32" s="6" t="n"/>
       <c r="E32" s="8" t="n"/>
-      <c r="F32" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G32" s="7" t="n"/>
-    </row>
-    <row r="33">
+      <c r="F32" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
       <c r="A33" s="6" t="n"/>
       <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="n"/>
+      <c r="D33" s="6" t="n"/>
       <c r="E33" s="8" t="n"/>
-      <c r="F33" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G33" s="7" t="n"/>
-    </row>
-    <row r="34">
+      <c r="F33" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
       <c r="A34" s="6" t="n"/>
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="n"/>
+      <c r="D34" s="6" t="n"/>
       <c r="E34" s="8" t="n"/>
-      <c r="F34" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G34" s="7" t="n"/>
-    </row>
-    <row r="35">
+      <c r="F34" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
       <c r="A35" s="6" t="n"/>
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
-      <c r="D35" s="7" t="n"/>
+      <c r="D35" s="6" t="n"/>
       <c r="E35" s="8" t="n"/>
-      <c r="F35" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G35" s="7" t="n"/>
-    </row>
-    <row r="36">
+      <c r="F35" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
       <c r="A36" s="6" t="n"/>
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
-      <c r="D36" s="7" t="n"/>
+      <c r="D36" s="6" t="n"/>
       <c r="E36" s="8" t="n"/>
-      <c r="F36" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G36" s="7" t="n"/>
-    </row>
-    <row r="37">
+      <c r="F36" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
       <c r="A37" s="6" t="n"/>
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
-      <c r="D37" s="7" t="n"/>
+      <c r="D37" s="6" t="n"/>
       <c r="E37" s="8" t="n"/>
-      <c r="F37" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G37" s="7" t="n"/>
-    </row>
-    <row r="38">
+      <c r="F37" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
       <c r="A38" s="6" t="n"/>
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="n"/>
+      <c r="D38" s="6" t="n"/>
       <c r="E38" s="8" t="n"/>
-      <c r="F38" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G38" s="7" t="n"/>
-    </row>
-    <row r="39">
+      <c r="F38" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
       <c r="A39" s="6" t="n"/>
       <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
-      <c r="D39" s="7" t="n"/>
+      <c r="D39" s="6" t="n"/>
       <c r="E39" s="8" t="n"/>
-      <c r="F39" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G39" s="7" t="n"/>
-    </row>
-    <row r="40">
+      <c r="F39" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
       <c r="A40" s="6" t="n"/>
       <c r="B40" s="7" t="n"/>
       <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="n"/>
+      <c r="D40" s="6" t="n"/>
       <c r="E40" s="8" t="n"/>
-      <c r="F40" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G40" s="7" t="n"/>
-    </row>
-    <row r="41">
+      <c r="F40" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
       <c r="A41" s="6" t="n"/>
       <c r="B41" s="7" t="n"/>
       <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="n"/>
+      <c r="D41" s="6" t="n"/>
       <c r="E41" s="8" t="n"/>
-      <c r="F41" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G41" s="7" t="n"/>
-    </row>
-    <row r="42">
+      <c r="F41" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
       <c r="A42" s="6" t="n"/>
       <c r="B42" s="7" t="n"/>
       <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="n"/>
+      <c r="D42" s="6" t="n"/>
       <c r="E42" s="8" t="n"/>
-      <c r="F42" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G42" s="7" t="n"/>
-    </row>
-    <row r="43">
+      <c r="F42" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
       <c r="A43" s="6" t="n"/>
       <c r="B43" s="7" t="n"/>
       <c r="C43" s="7" t="n"/>
-      <c r="D43" s="7" t="n"/>
+      <c r="D43" s="6" t="n"/>
       <c r="E43" s="8" t="n"/>
-      <c r="F43" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G43" s="7" t="n"/>
-    </row>
-    <row r="44">
+      <c r="F43" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
       <c r="A44" s="6" t="n"/>
       <c r="B44" s="7" t="n"/>
       <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="n"/>
+      <c r="D44" s="6" t="n"/>
       <c r="E44" s="8" t="n"/>
-      <c r="F44" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G44" s="7" t="n"/>
-    </row>
-    <row r="45">
+      <c r="F44" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
       <c r="A45" s="6" t="n"/>
       <c r="B45" s="7" t="n"/>
       <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="n"/>
+      <c r="D45" s="6" t="n"/>
       <c r="E45" s="8" t="n"/>
-      <c r="F45" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G45" s="7" t="n"/>
-    </row>
-    <row r="46">
+      <c r="F45" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
       <c r="A46" s="6" t="n"/>
       <c r="B46" s="7" t="n"/>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="7" t="n"/>
+      <c r="D46" s="6" t="n"/>
       <c r="E46" s="8" t="n"/>
-      <c r="F46" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G46" s="7" t="n"/>
-    </row>
-    <row r="47">
+      <c r="F46" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
       <c r="A47" s="6" t="n"/>
       <c r="B47" s="7" t="n"/>
       <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="n"/>
+      <c r="D47" s="6" t="n"/>
       <c r="E47" s="8" t="n"/>
-      <c r="F47" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G47" s="7" t="n"/>
-    </row>
-    <row r="48">
+      <c r="F47" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
       <c r="A48" s="6" t="n"/>
       <c r="B48" s="7" t="n"/>
       <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="n"/>
+      <c r="D48" s="6" t="n"/>
       <c r="E48" s="8" t="n"/>
-      <c r="F48" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G48" s="7" t="n"/>
-    </row>
-    <row r="49">
+      <c r="F48" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
       <c r="A49" s="6" t="n"/>
       <c r="B49" s="7" t="n"/>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="n"/>
+      <c r="D49" s="6" t="n"/>
       <c r="E49" s="8" t="n"/>
-      <c r="F49" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G49" s="7" t="n"/>
-    </row>
-    <row r="50">
+      <c r="F49" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
       <c r="A50" s="6" t="n"/>
       <c r="B50" s="7" t="n"/>
       <c r="C50" s="7" t="n"/>
-      <c r="D50" s="7" t="n"/>
+      <c r="D50" s="6" t="n"/>
       <c r="E50" s="8" t="n"/>
-      <c r="F50" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G50" s="7" t="n"/>
-    </row>
-    <row r="51">
+      <c r="F50" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
       <c r="A51" s="6" t="n"/>
       <c r="B51" s="7" t="n"/>
       <c r="C51" s="7" t="n"/>
-      <c r="D51" s="7" t="n"/>
+      <c r="D51" s="6" t="n"/>
       <c r="E51" s="8" t="n"/>
-      <c r="F51" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G51" s="7" t="n"/>
-    </row>
-    <row r="52">
+      <c r="F51" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
       <c r="A52" s="6" t="n"/>
       <c r="B52" s="7" t="n"/>
       <c r="C52" s="7" t="n"/>
-      <c r="D52" s="7" t="n"/>
+      <c r="D52" s="6" t="n"/>
       <c r="E52" s="8" t="n"/>
-      <c r="F52" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G52" s="7" t="n"/>
-    </row>
-    <row r="53">
+      <c r="F52" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
       <c r="A53" s="6" t="n"/>
       <c r="B53" s="7" t="n"/>
       <c r="C53" s="7" t="n"/>
-      <c r="D53" s="7" t="n"/>
+      <c r="D53" s="6" t="n"/>
       <c r="E53" s="8" t="n"/>
-      <c r="F53" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G53" s="7" t="n"/>
-    </row>
-    <row r="54">
+      <c r="F53" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
       <c r="A54" s="6" t="n"/>
       <c r="B54" s="7" t="n"/>
       <c r="C54" s="7" t="n"/>
-      <c r="D54" s="7" t="n"/>
+      <c r="D54" s="6" t="n"/>
       <c r="E54" s="8" t="n"/>
-      <c r="F54" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G54" s="7" t="n"/>
-    </row>
-    <row r="55">
+      <c r="F54" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
       <c r="A55" s="6" t="n"/>
       <c r="B55" s="7" t="n"/>
       <c r="C55" s="7" t="n"/>
-      <c r="D55" s="7" t="n"/>
+      <c r="D55" s="6" t="n"/>
       <c r="E55" s="8" t="n"/>
-      <c r="F55" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G55" s="7" t="n"/>
-    </row>
-    <row r="56">
+      <c r="F55" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
       <c r="A56" s="6" t="n"/>
       <c r="B56" s="7" t="n"/>
       <c r="C56" s="7" t="n"/>
-      <c r="D56" s="7" t="n"/>
+      <c r="D56" s="6" t="n"/>
       <c r="E56" s="8" t="n"/>
-      <c r="F56" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G56" s="7" t="n"/>
-    </row>
-    <row r="57">
+      <c r="F56" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
       <c r="A57" s="6" t="n"/>
       <c r="B57" s="7" t="n"/>
       <c r="C57" s="7" t="n"/>
-      <c r="D57" s="7" t="n"/>
+      <c r="D57" s="6" t="n"/>
       <c r="E57" s="8" t="n"/>
-      <c r="F57" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G57" s="7" t="n"/>
-    </row>
-    <row r="58">
+      <c r="F57" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
       <c r="A58" s="6" t="n"/>
       <c r="B58" s="7" t="n"/>
       <c r="C58" s="7" t="n"/>
-      <c r="D58" s="7" t="n"/>
+      <c r="D58" s="6" t="n"/>
       <c r="E58" s="8" t="n"/>
-      <c r="F58" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G58" s="7" t="n"/>
-    </row>
-    <row r="59">
+      <c r="F58" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
       <c r="A59" s="6" t="n"/>
       <c r="B59" s="7" t="n"/>
       <c r="C59" s="7" t="n"/>
-      <c r="D59" s="7" t="n"/>
+      <c r="D59" s="6" t="n"/>
       <c r="E59" s="8" t="n"/>
-      <c r="F59" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G59" s="7" t="n"/>
-    </row>
-    <row r="60">
+      <c r="F59" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
       <c r="A60" s="6" t="n"/>
       <c r="B60" s="7" t="n"/>
       <c r="C60" s="7" t="n"/>
-      <c r="D60" s="7" t="n"/>
+      <c r="D60" s="6" t="n"/>
       <c r="E60" s="8" t="n"/>
-      <c r="F60" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G60" s="7" t="n"/>
-    </row>
-    <row r="61">
+      <c r="F60" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
       <c r="A61" s="6" t="n"/>
       <c r="B61" s="7" t="n"/>
       <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="n"/>
+      <c r="D61" s="6" t="n"/>
       <c r="E61" s="8" t="n"/>
-      <c r="F61" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G61" s="7" t="n"/>
-    </row>
-    <row r="62">
+      <c r="F61" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
       <c r="A62" s="6" t="n"/>
       <c r="B62" s="7" t="n"/>
       <c r="C62" s="7" t="n"/>
-      <c r="D62" s="7" t="n"/>
+      <c r="D62" s="6" t="n"/>
       <c r="E62" s="8" t="n"/>
-      <c r="F62" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G62" s="7" t="n"/>
-    </row>
-    <row r="63">
+      <c r="F62" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
       <c r="A63" s="6" t="n"/>
       <c r="B63" s="7" t="n"/>
       <c r="C63" s="7" t="n"/>
-      <c r="D63" s="7" t="n"/>
+      <c r="D63" s="6" t="n"/>
       <c r="E63" s="8" t="n"/>
-      <c r="F63" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G63" s="7" t="n"/>
-    </row>
-    <row r="64">
+      <c r="F63" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1">
       <c r="A64" s="6" t="n"/>
       <c r="B64" s="7" t="n"/>
       <c r="C64" s="7" t="n"/>
-      <c r="D64" s="7" t="n"/>
+      <c r="D64" s="6" t="n"/>
       <c r="E64" s="8" t="n"/>
-      <c r="F64" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G64" s="7" t="n"/>
-    </row>
-    <row r="65">
+      <c r="F64" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
       <c r="A65" s="6" t="n"/>
       <c r="B65" s="7" t="n"/>
       <c r="C65" s="7" t="n"/>
-      <c r="D65" s="7" t="n"/>
+      <c r="D65" s="6" t="n"/>
       <c r="E65" s="8" t="n"/>
-      <c r="F65" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G65" s="7" t="n"/>
-    </row>
-    <row r="66">
+      <c r="F65" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1">
       <c r="A66" s="6" t="n"/>
       <c r="B66" s="7" t="n"/>
       <c r="C66" s="7" t="n"/>
-      <c r="D66" s="7" t="n"/>
+      <c r="D66" s="6" t="n"/>
       <c r="E66" s="8" t="n"/>
-      <c r="F66" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G66" s="7" t="n"/>
-    </row>
-    <row r="67">
+      <c r="F66" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
       <c r="A67" s="6" t="n"/>
       <c r="B67" s="7" t="n"/>
       <c r="C67" s="7" t="n"/>
-      <c r="D67" s="7" t="n"/>
+      <c r="D67" s="6" t="n"/>
       <c r="E67" s="8" t="n"/>
-      <c r="F67" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G67" s="7" t="n"/>
-    </row>
-    <row r="68">
+      <c r="F67" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
       <c r="A68" s="6" t="n"/>
       <c r="B68" s="7" t="n"/>
       <c r="C68" s="7" t="n"/>
-      <c r="D68" s="7" t="n"/>
+      <c r="D68" s="6" t="n"/>
       <c r="E68" s="8" t="n"/>
-      <c r="F68" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G68" s="7" t="n"/>
-    </row>
-    <row r="69">
+      <c r="F68" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1">
       <c r="A69" s="6" t="n"/>
       <c r="B69" s="7" t="n"/>
       <c r="C69" s="7" t="n"/>
-      <c r="D69" s="7" t="n"/>
+      <c r="D69" s="6" t="n"/>
       <c r="E69" s="8" t="n"/>
-      <c r="F69" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G69" s="7" t="n"/>
-    </row>
-    <row r="70">
+      <c r="F69" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1">
       <c r="A70" s="6" t="n"/>
       <c r="B70" s="7" t="n"/>
       <c r="C70" s="7" t="n"/>
-      <c r="D70" s="7" t="n"/>
+      <c r="D70" s="6" t="n"/>
       <c r="E70" s="8" t="n"/>
-      <c r="F70" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G70" s="7" t="n"/>
-    </row>
-    <row r="71">
+      <c r="F70" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1">
       <c r="A71" s="6" t="n"/>
       <c r="B71" s="7" t="n"/>
       <c r="C71" s="7" t="n"/>
-      <c r="D71" s="7" t="n"/>
+      <c r="D71" s="6" t="n"/>
       <c r="E71" s="8" t="n"/>
-      <c r="F71" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G71" s="7" t="n"/>
-    </row>
-    <row r="72">
+      <c r="F71" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="18" customHeight="1">
       <c r="A72" s="6" t="n"/>
       <c r="B72" s="7" t="n"/>
       <c r="C72" s="7" t="n"/>
-      <c r="D72" s="7" t="n"/>
+      <c r="D72" s="6" t="n"/>
       <c r="E72" s="8" t="n"/>
-      <c r="F72" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G72" s="7" t="n"/>
-    </row>
-    <row r="73">
+      <c r="F72" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1">
       <c r="A73" s="6" t="n"/>
       <c r="B73" s="7" t="n"/>
       <c r="C73" s="7" t="n"/>
-      <c r="D73" s="7" t="n"/>
+      <c r="D73" s="6" t="n"/>
       <c r="E73" s="8" t="n"/>
-      <c r="F73" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G73" s="7" t="n"/>
-    </row>
-    <row r="74">
+      <c r="F73" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
       <c r="A74" s="6" t="n"/>
       <c r="B74" s="7" t="n"/>
       <c r="C74" s="7" t="n"/>
-      <c r="D74" s="7" t="n"/>
+      <c r="D74" s="6" t="n"/>
       <c r="E74" s="8" t="n"/>
-      <c r="F74" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G74" s="7" t="n"/>
-    </row>
-    <row r="75">
+      <c r="F74" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="18" customHeight="1">
       <c r="A75" s="6" t="n"/>
       <c r="B75" s="7" t="n"/>
       <c r="C75" s="7" t="n"/>
-      <c r="D75" s="7" t="n"/>
+      <c r="D75" s="6" t="n"/>
       <c r="E75" s="8" t="n"/>
-      <c r="F75" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G75" s="7" t="n"/>
-    </row>
-    <row r="76">
+      <c r="F75" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1">
       <c r="A76" s="6" t="n"/>
       <c r="B76" s="7" t="n"/>
       <c r="C76" s="7" t="n"/>
-      <c r="D76" s="7" t="n"/>
+      <c r="D76" s="6" t="n"/>
       <c r="E76" s="8" t="n"/>
-      <c r="F76" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G76" s="7" t="n"/>
-    </row>
-    <row r="77">
+      <c r="F76" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="18" customHeight="1">
       <c r="A77" s="6" t="n"/>
       <c r="B77" s="7" t="n"/>
       <c r="C77" s="7" t="n"/>
-      <c r="D77" s="7" t="n"/>
+      <c r="D77" s="6" t="n"/>
       <c r="E77" s="8" t="n"/>
-      <c r="F77" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G77" s="7" t="n"/>
-    </row>
-    <row r="78">
+      <c r="F77" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="18" customHeight="1">
       <c r="A78" s="6" t="n"/>
       <c r="B78" s="7" t="n"/>
       <c r="C78" s="7" t="n"/>
-      <c r="D78" s="7" t="n"/>
+      <c r="D78" s="6" t="n"/>
       <c r="E78" s="8" t="n"/>
-      <c r="F78" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G78" s="7" t="n"/>
-    </row>
-    <row r="79">
+      <c r="F78" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
       <c r="A79" s="6" t="n"/>
       <c r="B79" s="7" t="n"/>
       <c r="C79" s="7" t="n"/>
-      <c r="D79" s="7" t="n"/>
+      <c r="D79" s="6" t="n"/>
       <c r="E79" s="8" t="n"/>
-      <c r="F79" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G79" s="7" t="n"/>
-    </row>
-    <row r="80">
+      <c r="F79" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1">
       <c r="A80" s="6" t="n"/>
       <c r="B80" s="7" t="n"/>
       <c r="C80" s="7" t="n"/>
-      <c r="D80" s="7" t="n"/>
+      <c r="D80" s="6" t="n"/>
       <c r="E80" s="8" t="n"/>
-      <c r="F80" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G80" s="7" t="n"/>
-    </row>
-    <row r="81">
+      <c r="F80" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="18" customHeight="1">
       <c r="A81" s="6" t="n"/>
       <c r="B81" s="7" t="n"/>
       <c r="C81" s="7" t="n"/>
-      <c r="D81" s="7" t="n"/>
+      <c r="D81" s="6" t="n"/>
       <c r="E81" s="8" t="n"/>
-      <c r="F81" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G81" s="7" t="n"/>
-    </row>
-    <row r="82">
+      <c r="F81" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="18" customHeight="1">
       <c r="A82" s="6" t="n"/>
       <c r="B82" s="7" t="n"/>
       <c r="C82" s="7" t="n"/>
-      <c r="D82" s="7" t="n"/>
+      <c r="D82" s="6" t="n"/>
       <c r="E82" s="8" t="n"/>
-      <c r="F82" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G82" s="7" t="n"/>
-    </row>
-    <row r="83">
+      <c r="F82" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="18" customHeight="1">
       <c r="A83" s="6" t="n"/>
       <c r="B83" s="7" t="n"/>
       <c r="C83" s="7" t="n"/>
-      <c r="D83" s="7" t="n"/>
+      <c r="D83" s="6" t="n"/>
       <c r="E83" s="8" t="n"/>
-      <c r="F83" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G83" s="7" t="n"/>
-    </row>
-    <row r="84">
+      <c r="F83" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1">
       <c r="A84" s="6" t="n"/>
       <c r="B84" s="7" t="n"/>
       <c r="C84" s="7" t="n"/>
-      <c r="D84" s="7" t="n"/>
+      <c r="D84" s="6" t="n"/>
       <c r="E84" s="8" t="n"/>
-      <c r="F84" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G84" s="7" t="n"/>
-    </row>
-    <row r="85">
+      <c r="F84" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="18" customHeight="1">
       <c r="A85" s="6" t="n"/>
       <c r="B85" s="7" t="n"/>
       <c r="C85" s="7" t="n"/>
-      <c r="D85" s="7" t="n"/>
+      <c r="D85" s="6" t="n"/>
       <c r="E85" s="8" t="n"/>
-      <c r="F85" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G85" s="7" t="n"/>
-    </row>
-    <row r="86">
+      <c r="F85" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1">
       <c r="A86" s="6" t="n"/>
       <c r="B86" s="7" t="n"/>
       <c r="C86" s="7" t="n"/>
-      <c r="D86" s="7" t="n"/>
+      <c r="D86" s="6" t="n"/>
       <c r="E86" s="8" t="n"/>
-      <c r="F86" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G86" s="7" t="n"/>
-    </row>
-    <row r="87">
+      <c r="F86" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="18" customHeight="1">
       <c r="A87" s="6" t="n"/>
       <c r="B87" s="7" t="n"/>
       <c r="C87" s="7" t="n"/>
-      <c r="D87" s="7" t="n"/>
+      <c r="D87" s="6" t="n"/>
       <c r="E87" s="8" t="n"/>
-      <c r="F87" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G87" s="7" t="n"/>
-    </row>
-    <row r="88">
+      <c r="F87" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="18" customHeight="1">
       <c r="A88" s="6" t="n"/>
       <c r="B88" s="7" t="n"/>
       <c r="C88" s="7" t="n"/>
-      <c r="D88" s="7" t="n"/>
+      <c r="D88" s="6" t="n"/>
       <c r="E88" s="8" t="n"/>
-      <c r="F88" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G88" s="7" t="n"/>
-    </row>
-    <row r="89">
+      <c r="F88" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="18" customHeight="1">
       <c r="A89" s="6" t="n"/>
       <c r="B89" s="7" t="n"/>
       <c r="C89" s="7" t="n"/>
-      <c r="D89" s="7" t="n"/>
+      <c r="D89" s="6" t="n"/>
       <c r="E89" s="8" t="n"/>
-      <c r="F89" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G89" s="7" t="n"/>
-    </row>
-    <row r="90">
+      <c r="F89" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1">
       <c r="A90" s="6" t="n"/>
       <c r="B90" s="7" t="n"/>
       <c r="C90" s="7" t="n"/>
-      <c r="D90" s="7" t="n"/>
+      <c r="D90" s="6" t="n"/>
       <c r="E90" s="8" t="n"/>
-      <c r="F90" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G90" s="7" t="n"/>
-    </row>
-    <row r="91">
+      <c r="F90" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="18" customHeight="1">
       <c r="A91" s="6" t="n"/>
       <c r="B91" s="7" t="n"/>
       <c r="C91" s="7" t="n"/>
-      <c r="D91" s="7" t="n"/>
+      <c r="D91" s="6" t="n"/>
       <c r="E91" s="8" t="n"/>
-      <c r="F91" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G91" s="7" t="n"/>
-    </row>
-    <row r="92">
+      <c r="F91" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="18" customHeight="1">
       <c r="A92" s="6" t="n"/>
       <c r="B92" s="7" t="n"/>
       <c r="C92" s="7" t="n"/>
-      <c r="D92" s="7" t="n"/>
+      <c r="D92" s="6" t="n"/>
       <c r="E92" s="8" t="n"/>
-      <c r="F92" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G92" s="7" t="n"/>
-    </row>
-    <row r="93">
+      <c r="F92" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
       <c r="A93" s="6" t="n"/>
       <c r="B93" s="7" t="n"/>
       <c r="C93" s="7" t="n"/>
-      <c r="D93" s="7" t="n"/>
+      <c r="D93" s="6" t="n"/>
       <c r="E93" s="8" t="n"/>
-      <c r="F93" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G93" s="7" t="n"/>
-    </row>
-    <row r="94">
+      <c r="F93" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="18" customHeight="1">
       <c r="A94" s="6" t="n"/>
       <c r="B94" s="7" t="n"/>
       <c r="C94" s="7" t="n"/>
-      <c r="D94" s="7" t="n"/>
+      <c r="D94" s="6" t="n"/>
       <c r="E94" s="8" t="n"/>
-      <c r="F94" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G94" s="7" t="n"/>
-    </row>
-    <row r="95">
+      <c r="F94" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
       <c r="A95" s="6" t="n"/>
       <c r="B95" s="7" t="n"/>
       <c r="C95" s="7" t="n"/>
-      <c r="D95" s="7" t="n"/>
+      <c r="D95" s="6" t="n"/>
       <c r="E95" s="8" t="n"/>
-      <c r="F95" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G95" s="7" t="n"/>
-    </row>
-    <row r="96">
+      <c r="F95" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="18" customHeight="1">
       <c r="A96" s="6" t="n"/>
       <c r="B96" s="7" t="n"/>
       <c r="C96" s="7" t="n"/>
-      <c r="D96" s="7" t="n"/>
+      <c r="D96" s="6" t="n"/>
       <c r="E96" s="8" t="n"/>
-      <c r="F96" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G96" s="7" t="n"/>
-    </row>
-    <row r="97">
+      <c r="F96" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1">
       <c r="A97" s="6" t="n"/>
       <c r="B97" s="7" t="n"/>
       <c r="C97" s="7" t="n"/>
-      <c r="D97" s="7" t="n"/>
+      <c r="D97" s="6" t="n"/>
       <c r="E97" s="8" t="n"/>
-      <c r="F97" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G97" s="7" t="n"/>
-    </row>
-    <row r="98">
+      <c r="F97" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="18" customHeight="1">
       <c r="A98" s="6" t="n"/>
       <c r="B98" s="7" t="n"/>
       <c r="C98" s="7" t="n"/>
-      <c r="D98" s="7" t="n"/>
+      <c r="D98" s="6" t="n"/>
       <c r="E98" s="8" t="n"/>
-      <c r="F98" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G98" s="7" t="n"/>
-    </row>
-    <row r="99">
+      <c r="F98" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="18" customHeight="1">
       <c r="A99" s="6" t="n"/>
       <c r="B99" s="7" t="n"/>
       <c r="C99" s="7" t="n"/>
-      <c r="D99" s="7" t="n"/>
+      <c r="D99" s="6" t="n"/>
       <c r="E99" s="8" t="n"/>
-      <c r="F99" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G99" s="7" t="n"/>
-    </row>
-    <row r="100">
+      <c r="F99" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="18" customHeight="1">
       <c r="A100" s="6" t="n"/>
       <c r="B100" s="7" t="n"/>
       <c r="C100" s="7" t="n"/>
-      <c r="D100" s="7" t="n"/>
+      <c r="D100" s="6" t="n"/>
       <c r="E100" s="8" t="n"/>
-      <c r="F100" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G100" s="7" t="n"/>
-    </row>
-    <row r="101">
+      <c r="F100" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="18" customHeight="1">
       <c r="A101" s="6" t="n"/>
       <c r="B101" s="7" t="n"/>
       <c r="C101" s="7" t="n"/>
-      <c r="D101" s="7" t="n"/>
+      <c r="D101" s="6" t="n"/>
       <c r="E101" s="8" t="n"/>
-      <c r="F101" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G101" s="7" t="n"/>
-    </row>
-    <row r="102">
+      <c r="F101" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="18" customHeight="1">
       <c r="A102" s="6" t="n"/>
       <c r="B102" s="7" t="n"/>
       <c r="C102" s="7" t="n"/>
-      <c r="D102" s="7" t="n"/>
+      <c r="D102" s="6" t="n"/>
       <c r="E102" s="8" t="n"/>
-      <c r="F102" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G102" s="7" t="n"/>
-    </row>
-    <row r="103">
+      <c r="F102" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="18" customHeight="1">
       <c r="A103" s="6" t="n"/>
       <c r="B103" s="7" t="n"/>
       <c r="C103" s="7" t="n"/>
-      <c r="D103" s="7" t="n"/>
+      <c r="D103" s="6" t="n"/>
       <c r="E103" s="8" t="n"/>
-      <c r="F103" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G103" s="7" t="n"/>
-    </row>
-    <row r="104">
+      <c r="F103" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G103" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="18" customHeight="1">
       <c r="A104" s="6" t="n"/>
       <c r="B104" s="7" t="n"/>
       <c r="C104" s="7" t="n"/>
-      <c r="D104" s="7" t="n"/>
+      <c r="D104" s="6" t="n"/>
       <c r="E104" s="8" t="n"/>
-      <c r="F104" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G104" s="7" t="n"/>
+      <c r="F104" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="G5:G104" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor inválido" error="Digite SIM ou NÃO" type="list">
+  <dataValidations count="3">
+    <dataValidation sqref="G5:G104" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Digite SIM ou NÃO" type="list">
       <formula1>"SIM,NÃO"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5:F104" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Horas inválidas" error="Digite entre 1 e 24" type="decimal" operator="between">
+    <dataValidation sqref="F5:F104" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Horas inválidas" error="Digite entre 1 e 24" type="decimal" operator="between">
       <formula1>1</formula1>
       <formula2>24</formula2>
+    </dataValidation>
+    <dataValidation sqref="E5:E104" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Custo inválido" error="Digite um valor &gt;= 0" type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1815,7 +2228,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2067,168 +2480,161 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="80" customWidth="1" min="1" max="1"/>
+    <col width="85" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
           <t>INSTRUÇÕES DE PREENCHIMENTO</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="8" customHeight="1">
+    <row r="2" ht="6" customHeight="1">
       <c r="A2" s="16" t="inlineStr"/>
     </row>
-    <row r="3" ht="20" customHeight="1">
+    <row r="3" ht="22" customHeight="1">
       <c r="A3" s="17" t="inlineStr">
         <is>
-          <t>1. CAMPOS OBRIGATÓRIOS (fundo rosa)</t>
+          <t>CAMPOS OBRIGATÓRIOS (fundo rosa)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • Nome Completo: Informe o nome completo do funcionário.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="8" customHeight="1">
-      <c r="A5" s="16" t="inlineStr"/>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>2. CAMPOS OPCIONAIS (fundo azul claro)</t>
+          <t xml:space="preserve">  • Nome Completo: Nome completo do funcionário.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Cargo / Função: Função que o funcionário exerce na empresa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Custo por Hora (R$): Valor em reais por hora trabalhada.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • E-mail: E-mail profissional do funcionário.</t>
+          <t xml:space="preserve">  • Horas por Dia Útil: Padrão = 9h. Aceita valores entre 1 e 24.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • Telefone: Formato sugerido: (37) 99999-9999</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • Cargo / Função: Consulte a aba 'Cargos de Referência' para sugestões.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • Custo por Hora: Valor em R$ (use ponto ou vírgula como decimal).</t>
+          <t xml:space="preserve">  • Ativo (SIM/NÃO): SIM = funcionário ativo, NÃO = inativo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="6" customHeight="1">
+      <c r="A9" s="16" t="inlineStr"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>CAMPOS OPCIONAIS (fundo azul)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • Horas por Dia Útil: Padrão = 9 horas. Aceita valores entre 1 e 24.</t>
+          <t xml:space="preserve">  • E-mail: E-mail profissional do funcionário.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • Ativo: Digite SIM (funcionário ativo) ou NÃO (inativo). Padrão = SIM.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="8" customHeight="1">
+          <t xml:space="preserve">  • Telefone: Formato sugerido: (37) 99999-9999</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="6" customHeight="1">
       <c r="A13" s="16" t="inlineStr"/>
     </row>
-    <row r="14" ht="20" customHeight="1">
+    <row r="14" ht="22" customHeight="1">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>3. COMO IMPORTAR</t>
+          <t>COMO IMPORTAR</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   1. Preencha os dados a partir da linha 5 (não altere as linhas 1-4).</t>
+          <t xml:space="preserve">  1. Preencha os dados a partir da linha 5 (não altere as linhas 1–4).</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   2. Salve o arquivo no formato .xlsx</t>
+          <t xml:space="preserve">  2. Salve no formato .xlsx</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   3. No sistema BCM, vá em Funcionários → botão 'Importar Excel'.</t>
+          <t xml:space="preserve">  3. No sistema → Funcionários → botão 'Importar Excel'.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   4. Selecione este arquivo e confirme a importação.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   5. O sistema validará os dados e importará todos os funcionários.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="8" customHeight="1">
-      <c r="A20" s="16" t="inlineStr"/>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="21" t="inlineStr">
-        <is>
-          <t>4. DICAS</t>
+          <t xml:space="preserve">  4. Revise a pré-visualização e confirme a importação.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="6" customHeight="1">
+      <c r="A19" s="16" t="inlineStr"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>OBSERVAÇÕES</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Não altere os cabeçalhos (linha 3) nem a estrutura das colunas.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • Não altere os cabeçalhos (linha 3) nem a estrutura das colunas.</t>
+          <t xml:space="preserve">  • A linha verde (linha 4) é apenas exemplo — não será importada.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • A linha verde (linha 4) é apenas um exemplo — não será importada.</t>
+          <t xml:space="preserve">  • Máximo de 100 funcionários por importação.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • Você pode importar até 100 funcionários por vez.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • Funcionários já cadastrados com o mesmo e-mail serão ignorados.</t>
+          <t xml:space="preserve">  • Consulte a aba 'Cargos de Referência' para sugestões de função.</t>
         </is>
       </c>
     </row>

--- a/docs/template_funcionarios.xlsx
+++ b/docs/template_funcionarios.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Funcionários" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Cargos de Referência" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Instruções" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Setores de Trabalho" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Cargos de Referência" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,18 +79,8 @@
       <color rgb="00475569"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00333333"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="13">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -137,21 +127,6 @@
         <fgColor rgb="00EDF1F7"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CC0000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00166534"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00854D0E"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -179,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -215,27 +190,6 @@
     <xf numFmtId="0" fontId="9" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -601,16 +555,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -650,15 +605,20 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>Setor de Trabalho *</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
           <t>Custo por Hora (R$) *</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Horas por Dia Útil *</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Ativo (SIM/NÃO) *</t>
         </is>
@@ -685,13 +645,18 @@
           <t>Eletricista Industrial</t>
         </is>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Montagem de Campo</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="F4" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -702,11 +667,12 @@
       <c r="B5" s="7" t="n"/>
       <c r="C5" s="7" t="n"/>
       <c r="D5" s="6" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -717,11 +683,12 @@
       <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="8" t="n"/>
-      <c r="F6" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -732,11 +699,12 @@
       <c r="B7" s="7" t="n"/>
       <c r="C7" s="7" t="n"/>
       <c r="D7" s="6" t="n"/>
-      <c r="E7" s="8" t="n"/>
-      <c r="F7" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -747,11 +715,12 @@
       <c r="B8" s="7" t="n"/>
       <c r="C8" s="7" t="n"/>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -762,11 +731,12 @@
       <c r="B9" s="7" t="n"/>
       <c r="C9" s="7" t="n"/>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -777,11 +747,12 @@
       <c r="B10" s="7" t="n"/>
       <c r="C10" s="7" t="n"/>
       <c r="D10" s="6" t="n"/>
-      <c r="E10" s="8" t="n"/>
-      <c r="F10" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -792,11 +763,12 @@
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="n"/>
-      <c r="E11" s="8" t="n"/>
-      <c r="F11" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -807,11 +779,12 @@
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
       <c r="D12" s="6" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -822,11 +795,12 @@
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="8" t="n"/>
-      <c r="F13" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -837,11 +811,12 @@
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
       <c r="D14" s="6" t="n"/>
-      <c r="E14" s="8" t="n"/>
-      <c r="F14" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -852,11 +827,12 @@
       <c r="B15" s="7" t="n"/>
       <c r="C15" s="7" t="n"/>
       <c r="D15" s="6" t="n"/>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="8" t="n"/>
+      <c r="G15" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -867,11 +843,12 @@
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
       <c r="D16" s="6" t="n"/>
-      <c r="E16" s="8" t="n"/>
-      <c r="F16" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -882,11 +859,12 @@
       <c r="B17" s="7" t="n"/>
       <c r="C17" s="7" t="n"/>
       <c r="D17" s="6" t="n"/>
-      <c r="E17" s="8" t="n"/>
-      <c r="F17" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -897,11 +875,12 @@
       <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="6" t="n"/>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -912,11 +891,12 @@
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
       <c r="D19" s="6" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -927,11 +907,12 @@
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
       <c r="D20" s="6" t="n"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -942,11 +923,12 @@
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
       <c r="D21" s="6" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="8" t="n"/>
+      <c r="G21" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -957,11 +939,12 @@
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
       <c r="D22" s="6" t="n"/>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -972,11 +955,12 @@
       <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
       <c r="D23" s="6" t="n"/>
-      <c r="E23" s="8" t="n"/>
-      <c r="F23" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="8" t="n"/>
+      <c r="G23" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -987,11 +971,12 @@
       <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
       <c r="D24" s="6" t="n"/>
-      <c r="E24" s="8" t="n"/>
-      <c r="F24" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1002,11 +987,12 @@
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="6" t="n"/>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="8" t="n"/>
+      <c r="G25" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1017,11 +1003,12 @@
       <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="n"/>
       <c r="D26" s="6" t="n"/>
-      <c r="E26" s="8" t="n"/>
-      <c r="F26" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1032,11 +1019,12 @@
       <c r="B27" s="7" t="n"/>
       <c r="C27" s="7" t="n"/>
       <c r="D27" s="6" t="n"/>
-      <c r="E27" s="8" t="n"/>
-      <c r="F27" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="8" t="n"/>
+      <c r="G27" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1047,11 +1035,12 @@
       <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
       <c r="D28" s="6" t="n"/>
-      <c r="E28" s="8" t="n"/>
-      <c r="F28" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1062,11 +1051,12 @@
       <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
       <c r="D29" s="6" t="n"/>
-      <c r="E29" s="8" t="n"/>
-      <c r="F29" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="8" t="n"/>
+      <c r="G29" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1077,11 +1067,12 @@
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
       <c r="D30" s="6" t="n"/>
-      <c r="E30" s="8" t="n"/>
-      <c r="F30" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="8" t="n"/>
+      <c r="G30" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1092,11 +1083,12 @@
       <c r="B31" s="7" t="n"/>
       <c r="C31" s="7" t="n"/>
       <c r="D31" s="6" t="n"/>
-      <c r="E31" s="8" t="n"/>
-      <c r="F31" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="8" t="n"/>
+      <c r="G31" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1107,11 +1099,12 @@
       <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
       <c r="D32" s="6" t="n"/>
-      <c r="E32" s="8" t="n"/>
-      <c r="F32" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="8" t="n"/>
+      <c r="G32" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1122,11 +1115,12 @@
       <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
       <c r="D33" s="6" t="n"/>
-      <c r="E33" s="8" t="n"/>
-      <c r="F33" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="8" t="n"/>
+      <c r="G33" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1137,11 +1131,12 @@
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
       <c r="D34" s="6" t="n"/>
-      <c r="E34" s="8" t="n"/>
-      <c r="F34" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="8" t="n"/>
+      <c r="G34" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1152,11 +1147,12 @@
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
       <c r="D35" s="6" t="n"/>
-      <c r="E35" s="8" t="n"/>
-      <c r="F35" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G35" s="6" t="inlineStr">
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="8" t="n"/>
+      <c r="G35" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1167,11 +1163,12 @@
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
       <c r="D36" s="6" t="n"/>
-      <c r="E36" s="8" t="n"/>
-      <c r="F36" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="8" t="n"/>
+      <c r="G36" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1182,11 +1179,12 @@
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
       <c r="D37" s="6" t="n"/>
-      <c r="E37" s="8" t="n"/>
-      <c r="F37" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G37" s="6" t="inlineStr">
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="8" t="n"/>
+      <c r="G37" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1197,11 +1195,12 @@
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
       <c r="D38" s="6" t="n"/>
-      <c r="E38" s="8" t="n"/>
-      <c r="F38" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G38" s="6" t="inlineStr">
+      <c r="E38" s="6" t="n"/>
+      <c r="F38" s="8" t="n"/>
+      <c r="G38" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1212,11 +1211,12 @@
       <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
       <c r="D39" s="6" t="n"/>
-      <c r="E39" s="8" t="n"/>
-      <c r="F39" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G39" s="6" t="inlineStr">
+      <c r="E39" s="6" t="n"/>
+      <c r="F39" s="8" t="n"/>
+      <c r="G39" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1227,11 +1227,12 @@
       <c r="B40" s="7" t="n"/>
       <c r="C40" s="7" t="n"/>
       <c r="D40" s="6" t="n"/>
-      <c r="E40" s="8" t="n"/>
-      <c r="F40" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="8" t="n"/>
+      <c r="G40" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1242,11 +1243,12 @@
       <c r="B41" s="7" t="n"/>
       <c r="C41" s="7" t="n"/>
       <c r="D41" s="6" t="n"/>
-      <c r="E41" s="8" t="n"/>
-      <c r="F41" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G41" s="6" t="inlineStr">
+      <c r="E41" s="6" t="n"/>
+      <c r="F41" s="8" t="n"/>
+      <c r="G41" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1257,11 +1259,12 @@
       <c r="B42" s="7" t="n"/>
       <c r="C42" s="7" t="n"/>
       <c r="D42" s="6" t="n"/>
-      <c r="E42" s="8" t="n"/>
-      <c r="F42" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G42" s="6" t="inlineStr">
+      <c r="E42" s="6" t="n"/>
+      <c r="F42" s="8" t="n"/>
+      <c r="G42" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1272,11 +1275,12 @@
       <c r="B43" s="7" t="n"/>
       <c r="C43" s="7" t="n"/>
       <c r="D43" s="6" t="n"/>
-      <c r="E43" s="8" t="n"/>
-      <c r="F43" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G43" s="6" t="inlineStr">
+      <c r="E43" s="6" t="n"/>
+      <c r="F43" s="8" t="n"/>
+      <c r="G43" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1287,11 +1291,12 @@
       <c r="B44" s="7" t="n"/>
       <c r="C44" s="7" t="n"/>
       <c r="D44" s="6" t="n"/>
-      <c r="E44" s="8" t="n"/>
-      <c r="F44" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G44" s="6" t="inlineStr">
+      <c r="E44" s="6" t="n"/>
+      <c r="F44" s="8" t="n"/>
+      <c r="G44" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1302,11 +1307,12 @@
       <c r="B45" s="7" t="n"/>
       <c r="C45" s="7" t="n"/>
       <c r="D45" s="6" t="n"/>
-      <c r="E45" s="8" t="n"/>
-      <c r="F45" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G45" s="6" t="inlineStr">
+      <c r="E45" s="6" t="n"/>
+      <c r="F45" s="8" t="n"/>
+      <c r="G45" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1317,11 +1323,12 @@
       <c r="B46" s="7" t="n"/>
       <c r="C46" s="7" t="n"/>
       <c r="D46" s="6" t="n"/>
-      <c r="E46" s="8" t="n"/>
-      <c r="F46" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G46" s="6" t="inlineStr">
+      <c r="E46" s="6" t="n"/>
+      <c r="F46" s="8" t="n"/>
+      <c r="G46" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1332,11 +1339,12 @@
       <c r="B47" s="7" t="n"/>
       <c r="C47" s="7" t="n"/>
       <c r="D47" s="6" t="n"/>
-      <c r="E47" s="8" t="n"/>
-      <c r="F47" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G47" s="6" t="inlineStr">
+      <c r="E47" s="6" t="n"/>
+      <c r="F47" s="8" t="n"/>
+      <c r="G47" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1347,11 +1355,12 @@
       <c r="B48" s="7" t="n"/>
       <c r="C48" s="7" t="n"/>
       <c r="D48" s="6" t="n"/>
-      <c r="E48" s="8" t="n"/>
-      <c r="F48" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G48" s="6" t="inlineStr">
+      <c r="E48" s="6" t="n"/>
+      <c r="F48" s="8" t="n"/>
+      <c r="G48" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1362,11 +1371,12 @@
       <c r="B49" s="7" t="n"/>
       <c r="C49" s="7" t="n"/>
       <c r="D49" s="6" t="n"/>
-      <c r="E49" s="8" t="n"/>
-      <c r="F49" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G49" s="6" t="inlineStr">
+      <c r="E49" s="6" t="n"/>
+      <c r="F49" s="8" t="n"/>
+      <c r="G49" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1377,11 +1387,12 @@
       <c r="B50" s="7" t="n"/>
       <c r="C50" s="7" t="n"/>
       <c r="D50" s="6" t="n"/>
-      <c r="E50" s="8" t="n"/>
-      <c r="F50" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
+      <c r="E50" s="6" t="n"/>
+      <c r="F50" s="8" t="n"/>
+      <c r="G50" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1392,11 +1403,12 @@
       <c r="B51" s="7" t="n"/>
       <c r="C51" s="7" t="n"/>
       <c r="D51" s="6" t="n"/>
-      <c r="E51" s="8" t="n"/>
-      <c r="F51" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G51" s="6" t="inlineStr">
+      <c r="E51" s="6" t="n"/>
+      <c r="F51" s="8" t="n"/>
+      <c r="G51" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1407,11 +1419,12 @@
       <c r="B52" s="7" t="n"/>
       <c r="C52" s="7" t="n"/>
       <c r="D52" s="6" t="n"/>
-      <c r="E52" s="8" t="n"/>
-      <c r="F52" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
+      <c r="E52" s="6" t="n"/>
+      <c r="F52" s="8" t="n"/>
+      <c r="G52" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1422,11 +1435,12 @@
       <c r="B53" s="7" t="n"/>
       <c r="C53" s="7" t="n"/>
       <c r="D53" s="6" t="n"/>
-      <c r="E53" s="8" t="n"/>
-      <c r="F53" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G53" s="6" t="inlineStr">
+      <c r="E53" s="6" t="n"/>
+      <c r="F53" s="8" t="n"/>
+      <c r="G53" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1437,11 +1451,12 @@
       <c r="B54" s="7" t="n"/>
       <c r="C54" s="7" t="n"/>
       <c r="D54" s="6" t="n"/>
-      <c r="E54" s="8" t="n"/>
-      <c r="F54" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G54" s="6" t="inlineStr">
+      <c r="E54" s="6" t="n"/>
+      <c r="F54" s="8" t="n"/>
+      <c r="G54" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1452,11 +1467,12 @@
       <c r="B55" s="7" t="n"/>
       <c r="C55" s="7" t="n"/>
       <c r="D55" s="6" t="n"/>
-      <c r="E55" s="8" t="n"/>
-      <c r="F55" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G55" s="6" t="inlineStr">
+      <c r="E55" s="6" t="n"/>
+      <c r="F55" s="8" t="n"/>
+      <c r="G55" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1467,11 +1483,12 @@
       <c r="B56" s="7" t="n"/>
       <c r="C56" s="7" t="n"/>
       <c r="D56" s="6" t="n"/>
-      <c r="E56" s="8" t="n"/>
-      <c r="F56" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
+      <c r="E56" s="6" t="n"/>
+      <c r="F56" s="8" t="n"/>
+      <c r="G56" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1482,11 +1499,12 @@
       <c r="B57" s="7" t="n"/>
       <c r="C57" s="7" t="n"/>
       <c r="D57" s="6" t="n"/>
-      <c r="E57" s="8" t="n"/>
-      <c r="F57" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G57" s="6" t="inlineStr">
+      <c r="E57" s="6" t="n"/>
+      <c r="F57" s="8" t="n"/>
+      <c r="G57" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1497,11 +1515,12 @@
       <c r="B58" s="7" t="n"/>
       <c r="C58" s="7" t="n"/>
       <c r="D58" s="6" t="n"/>
-      <c r="E58" s="8" t="n"/>
-      <c r="F58" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
+      <c r="E58" s="6" t="n"/>
+      <c r="F58" s="8" t="n"/>
+      <c r="G58" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1512,11 +1531,12 @@
       <c r="B59" s="7" t="n"/>
       <c r="C59" s="7" t="n"/>
       <c r="D59" s="6" t="n"/>
-      <c r="E59" s="8" t="n"/>
-      <c r="F59" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G59" s="6" t="inlineStr">
+      <c r="E59" s="6" t="n"/>
+      <c r="F59" s="8" t="n"/>
+      <c r="G59" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1527,11 +1547,12 @@
       <c r="B60" s="7" t="n"/>
       <c r="C60" s="7" t="n"/>
       <c r="D60" s="6" t="n"/>
-      <c r="E60" s="8" t="n"/>
-      <c r="F60" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G60" s="6" t="inlineStr">
+      <c r="E60" s="6" t="n"/>
+      <c r="F60" s="8" t="n"/>
+      <c r="G60" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1542,11 +1563,12 @@
       <c r="B61" s="7" t="n"/>
       <c r="C61" s="7" t="n"/>
       <c r="D61" s="6" t="n"/>
-      <c r="E61" s="8" t="n"/>
-      <c r="F61" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G61" s="6" t="inlineStr">
+      <c r="E61" s="6" t="n"/>
+      <c r="F61" s="8" t="n"/>
+      <c r="G61" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1557,11 +1579,12 @@
       <c r="B62" s="7" t="n"/>
       <c r="C62" s="7" t="n"/>
       <c r="D62" s="6" t="n"/>
-      <c r="E62" s="8" t="n"/>
-      <c r="F62" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G62" s="6" t="inlineStr">
+      <c r="E62" s="6" t="n"/>
+      <c r="F62" s="8" t="n"/>
+      <c r="G62" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1572,11 +1595,12 @@
       <c r="B63" s="7" t="n"/>
       <c r="C63" s="7" t="n"/>
       <c r="D63" s="6" t="n"/>
-      <c r="E63" s="8" t="n"/>
-      <c r="F63" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G63" s="6" t="inlineStr">
+      <c r="E63" s="6" t="n"/>
+      <c r="F63" s="8" t="n"/>
+      <c r="G63" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1587,11 +1611,12 @@
       <c r="B64" s="7" t="n"/>
       <c r="C64" s="7" t="n"/>
       <c r="D64" s="6" t="n"/>
-      <c r="E64" s="8" t="n"/>
-      <c r="F64" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G64" s="6" t="inlineStr">
+      <c r="E64" s="6" t="n"/>
+      <c r="F64" s="8" t="n"/>
+      <c r="G64" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1602,11 +1627,12 @@
       <c r="B65" s="7" t="n"/>
       <c r="C65" s="7" t="n"/>
       <c r="D65" s="6" t="n"/>
-      <c r="E65" s="8" t="n"/>
-      <c r="F65" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G65" s="6" t="inlineStr">
+      <c r="E65" s="6" t="n"/>
+      <c r="F65" s="8" t="n"/>
+      <c r="G65" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1617,11 +1643,12 @@
       <c r="B66" s="7" t="n"/>
       <c r="C66" s="7" t="n"/>
       <c r="D66" s="6" t="n"/>
-      <c r="E66" s="8" t="n"/>
-      <c r="F66" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G66" s="6" t="inlineStr">
+      <c r="E66" s="6" t="n"/>
+      <c r="F66" s="8" t="n"/>
+      <c r="G66" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1632,11 +1659,12 @@
       <c r="B67" s="7" t="n"/>
       <c r="C67" s="7" t="n"/>
       <c r="D67" s="6" t="n"/>
-      <c r="E67" s="8" t="n"/>
-      <c r="F67" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G67" s="6" t="inlineStr">
+      <c r="E67" s="6" t="n"/>
+      <c r="F67" s="8" t="n"/>
+      <c r="G67" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1647,11 +1675,12 @@
       <c r="B68" s="7" t="n"/>
       <c r="C68" s="7" t="n"/>
       <c r="D68" s="6" t="n"/>
-      <c r="E68" s="8" t="n"/>
-      <c r="F68" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G68" s="6" t="inlineStr">
+      <c r="E68" s="6" t="n"/>
+      <c r="F68" s="8" t="n"/>
+      <c r="G68" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1662,11 +1691,12 @@
       <c r="B69" s="7" t="n"/>
       <c r="C69" s="7" t="n"/>
       <c r="D69" s="6" t="n"/>
-      <c r="E69" s="8" t="n"/>
-      <c r="F69" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G69" s="6" t="inlineStr">
+      <c r="E69" s="6" t="n"/>
+      <c r="F69" s="8" t="n"/>
+      <c r="G69" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1677,11 +1707,12 @@
       <c r="B70" s="7" t="n"/>
       <c r="C70" s="7" t="n"/>
       <c r="D70" s="6" t="n"/>
-      <c r="E70" s="8" t="n"/>
-      <c r="F70" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G70" s="6" t="inlineStr">
+      <c r="E70" s="6" t="n"/>
+      <c r="F70" s="8" t="n"/>
+      <c r="G70" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1692,11 +1723,12 @@
       <c r="B71" s="7" t="n"/>
       <c r="C71" s="7" t="n"/>
       <c r="D71" s="6" t="n"/>
-      <c r="E71" s="8" t="n"/>
-      <c r="F71" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G71" s="6" t="inlineStr">
+      <c r="E71" s="6" t="n"/>
+      <c r="F71" s="8" t="n"/>
+      <c r="G71" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1707,11 +1739,12 @@
       <c r="B72" s="7" t="n"/>
       <c r="C72" s="7" t="n"/>
       <c r="D72" s="6" t="n"/>
-      <c r="E72" s="8" t="n"/>
-      <c r="F72" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G72" s="6" t="inlineStr">
+      <c r="E72" s="6" t="n"/>
+      <c r="F72" s="8" t="n"/>
+      <c r="G72" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1722,11 +1755,12 @@
       <c r="B73" s="7" t="n"/>
       <c r="C73" s="7" t="n"/>
       <c r="D73" s="6" t="n"/>
-      <c r="E73" s="8" t="n"/>
-      <c r="F73" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G73" s="6" t="inlineStr">
+      <c r="E73" s="6" t="n"/>
+      <c r="F73" s="8" t="n"/>
+      <c r="G73" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1737,11 +1771,12 @@
       <c r="B74" s="7" t="n"/>
       <c r="C74" s="7" t="n"/>
       <c r="D74" s="6" t="n"/>
-      <c r="E74" s="8" t="n"/>
-      <c r="F74" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G74" s="6" t="inlineStr">
+      <c r="E74" s="6" t="n"/>
+      <c r="F74" s="8" t="n"/>
+      <c r="G74" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H74" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1752,11 +1787,12 @@
       <c r="B75" s="7" t="n"/>
       <c r="C75" s="7" t="n"/>
       <c r="D75" s="6" t="n"/>
-      <c r="E75" s="8" t="n"/>
-      <c r="F75" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G75" s="6" t="inlineStr">
+      <c r="E75" s="6" t="n"/>
+      <c r="F75" s="8" t="n"/>
+      <c r="G75" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1767,11 +1803,12 @@
       <c r="B76" s="7" t="n"/>
       <c r="C76" s="7" t="n"/>
       <c r="D76" s="6" t="n"/>
-      <c r="E76" s="8" t="n"/>
-      <c r="F76" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G76" s="6" t="inlineStr">
+      <c r="E76" s="6" t="n"/>
+      <c r="F76" s="8" t="n"/>
+      <c r="G76" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1782,11 +1819,12 @@
       <c r="B77" s="7" t="n"/>
       <c r="C77" s="7" t="n"/>
       <c r="D77" s="6" t="n"/>
-      <c r="E77" s="8" t="n"/>
-      <c r="F77" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G77" s="6" t="inlineStr">
+      <c r="E77" s="6" t="n"/>
+      <c r="F77" s="8" t="n"/>
+      <c r="G77" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1797,11 +1835,12 @@
       <c r="B78" s="7" t="n"/>
       <c r="C78" s="7" t="n"/>
       <c r="D78" s="6" t="n"/>
-      <c r="E78" s="8" t="n"/>
-      <c r="F78" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G78" s="6" t="inlineStr">
+      <c r="E78" s="6" t="n"/>
+      <c r="F78" s="8" t="n"/>
+      <c r="G78" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1812,11 +1851,12 @@
       <c r="B79" s="7" t="n"/>
       <c r="C79" s="7" t="n"/>
       <c r="D79" s="6" t="n"/>
-      <c r="E79" s="8" t="n"/>
-      <c r="F79" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G79" s="6" t="inlineStr">
+      <c r="E79" s="6" t="n"/>
+      <c r="F79" s="8" t="n"/>
+      <c r="G79" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1827,11 +1867,12 @@
       <c r="B80" s="7" t="n"/>
       <c r="C80" s="7" t="n"/>
       <c r="D80" s="6" t="n"/>
-      <c r="E80" s="8" t="n"/>
-      <c r="F80" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G80" s="6" t="inlineStr">
+      <c r="E80" s="6" t="n"/>
+      <c r="F80" s="8" t="n"/>
+      <c r="G80" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1842,11 +1883,12 @@
       <c r="B81" s="7" t="n"/>
       <c r="C81" s="7" t="n"/>
       <c r="D81" s="6" t="n"/>
-      <c r="E81" s="8" t="n"/>
-      <c r="F81" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G81" s="6" t="inlineStr">
+      <c r="E81" s="6" t="n"/>
+      <c r="F81" s="8" t="n"/>
+      <c r="G81" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1857,11 +1899,12 @@
       <c r="B82" s="7" t="n"/>
       <c r="C82" s="7" t="n"/>
       <c r="D82" s="6" t="n"/>
-      <c r="E82" s="8" t="n"/>
-      <c r="F82" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G82" s="6" t="inlineStr">
+      <c r="E82" s="6" t="n"/>
+      <c r="F82" s="8" t="n"/>
+      <c r="G82" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1872,11 +1915,12 @@
       <c r="B83" s="7" t="n"/>
       <c r="C83" s="7" t="n"/>
       <c r="D83" s="6" t="n"/>
-      <c r="E83" s="8" t="n"/>
-      <c r="F83" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G83" s="6" t="inlineStr">
+      <c r="E83" s="6" t="n"/>
+      <c r="F83" s="8" t="n"/>
+      <c r="G83" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1887,11 +1931,12 @@
       <c r="B84" s="7" t="n"/>
       <c r="C84" s="7" t="n"/>
       <c r="D84" s="6" t="n"/>
-      <c r="E84" s="8" t="n"/>
-      <c r="F84" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G84" s="6" t="inlineStr">
+      <c r="E84" s="6" t="n"/>
+      <c r="F84" s="8" t="n"/>
+      <c r="G84" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H84" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1902,11 +1947,12 @@
       <c r="B85" s="7" t="n"/>
       <c r="C85" s="7" t="n"/>
       <c r="D85" s="6" t="n"/>
-      <c r="E85" s="8" t="n"/>
-      <c r="F85" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G85" s="6" t="inlineStr">
+      <c r="E85" s="6" t="n"/>
+      <c r="F85" s="8" t="n"/>
+      <c r="G85" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1917,11 +1963,12 @@
       <c r="B86" s="7" t="n"/>
       <c r="C86" s="7" t="n"/>
       <c r="D86" s="6" t="n"/>
-      <c r="E86" s="8" t="n"/>
-      <c r="F86" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G86" s="6" t="inlineStr">
+      <c r="E86" s="6" t="n"/>
+      <c r="F86" s="8" t="n"/>
+      <c r="G86" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1932,11 +1979,12 @@
       <c r="B87" s="7" t="n"/>
       <c r="C87" s="7" t="n"/>
       <c r="D87" s="6" t="n"/>
-      <c r="E87" s="8" t="n"/>
-      <c r="F87" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G87" s="6" t="inlineStr">
+      <c r="E87" s="6" t="n"/>
+      <c r="F87" s="8" t="n"/>
+      <c r="G87" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1947,11 +1995,12 @@
       <c r="B88" s="7" t="n"/>
       <c r="C88" s="7" t="n"/>
       <c r="D88" s="6" t="n"/>
-      <c r="E88" s="8" t="n"/>
-      <c r="F88" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G88" s="6" t="inlineStr">
+      <c r="E88" s="6" t="n"/>
+      <c r="F88" s="8" t="n"/>
+      <c r="G88" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1962,11 +2011,12 @@
       <c r="B89" s="7" t="n"/>
       <c r="C89" s="7" t="n"/>
       <c r="D89" s="6" t="n"/>
-      <c r="E89" s="8" t="n"/>
-      <c r="F89" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G89" s="6" t="inlineStr">
+      <c r="E89" s="6" t="n"/>
+      <c r="F89" s="8" t="n"/>
+      <c r="G89" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1977,11 +2027,12 @@
       <c r="B90" s="7" t="n"/>
       <c r="C90" s="7" t="n"/>
       <c r="D90" s="6" t="n"/>
-      <c r="E90" s="8" t="n"/>
-      <c r="F90" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G90" s="6" t="inlineStr">
+      <c r="E90" s="6" t="n"/>
+      <c r="F90" s="8" t="n"/>
+      <c r="G90" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H90" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1992,11 +2043,12 @@
       <c r="B91" s="7" t="n"/>
       <c r="C91" s="7" t="n"/>
       <c r="D91" s="6" t="n"/>
-      <c r="E91" s="8" t="n"/>
-      <c r="F91" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G91" s="6" t="inlineStr">
+      <c r="E91" s="6" t="n"/>
+      <c r="F91" s="8" t="n"/>
+      <c r="G91" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2007,11 +2059,12 @@
       <c r="B92" s="7" t="n"/>
       <c r="C92" s="7" t="n"/>
       <c r="D92" s="6" t="n"/>
-      <c r="E92" s="8" t="n"/>
-      <c r="F92" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G92" s="6" t="inlineStr">
+      <c r="E92" s="6" t="n"/>
+      <c r="F92" s="8" t="n"/>
+      <c r="G92" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H92" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2022,11 +2075,12 @@
       <c r="B93" s="7" t="n"/>
       <c r="C93" s="7" t="n"/>
       <c r="D93" s="6" t="n"/>
-      <c r="E93" s="8" t="n"/>
-      <c r="F93" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G93" s="6" t="inlineStr">
+      <c r="E93" s="6" t="n"/>
+      <c r="F93" s="8" t="n"/>
+      <c r="G93" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H93" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2037,11 +2091,12 @@
       <c r="B94" s="7" t="n"/>
       <c r="C94" s="7" t="n"/>
       <c r="D94" s="6" t="n"/>
-      <c r="E94" s="8" t="n"/>
-      <c r="F94" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G94" s="6" t="inlineStr">
+      <c r="E94" s="6" t="n"/>
+      <c r="F94" s="8" t="n"/>
+      <c r="G94" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H94" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2052,11 +2107,12 @@
       <c r="B95" s="7" t="n"/>
       <c r="C95" s="7" t="n"/>
       <c r="D95" s="6" t="n"/>
-      <c r="E95" s="8" t="n"/>
-      <c r="F95" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G95" s="6" t="inlineStr">
+      <c r="E95" s="6" t="n"/>
+      <c r="F95" s="8" t="n"/>
+      <c r="G95" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H95" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2067,11 +2123,12 @@
       <c r="B96" s="7" t="n"/>
       <c r="C96" s="7" t="n"/>
       <c r="D96" s="6" t="n"/>
-      <c r="E96" s="8" t="n"/>
-      <c r="F96" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G96" s="6" t="inlineStr">
+      <c r="E96" s="6" t="n"/>
+      <c r="F96" s="8" t="n"/>
+      <c r="G96" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H96" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2082,11 +2139,12 @@
       <c r="B97" s="7" t="n"/>
       <c r="C97" s="7" t="n"/>
       <c r="D97" s="6" t="n"/>
-      <c r="E97" s="8" t="n"/>
-      <c r="F97" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G97" s="6" t="inlineStr">
+      <c r="E97" s="6" t="n"/>
+      <c r="F97" s="8" t="n"/>
+      <c r="G97" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H97" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2097,11 +2155,12 @@
       <c r="B98" s="7" t="n"/>
       <c r="C98" s="7" t="n"/>
       <c r="D98" s="6" t="n"/>
-      <c r="E98" s="8" t="n"/>
-      <c r="F98" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G98" s="6" t="inlineStr">
+      <c r="E98" s="6" t="n"/>
+      <c r="F98" s="8" t="n"/>
+      <c r="G98" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H98" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2112,11 +2171,12 @@
       <c r="B99" s="7" t="n"/>
       <c r="C99" s="7" t="n"/>
       <c r="D99" s="6" t="n"/>
-      <c r="E99" s="8" t="n"/>
-      <c r="F99" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G99" s="6" t="inlineStr">
+      <c r="E99" s="6" t="n"/>
+      <c r="F99" s="8" t="n"/>
+      <c r="G99" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H99" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2127,11 +2187,12 @@
       <c r="B100" s="7" t="n"/>
       <c r="C100" s="7" t="n"/>
       <c r="D100" s="6" t="n"/>
-      <c r="E100" s="8" t="n"/>
-      <c r="F100" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G100" s="6" t="inlineStr">
+      <c r="E100" s="6" t="n"/>
+      <c r="F100" s="8" t="n"/>
+      <c r="G100" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H100" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2142,11 +2203,12 @@
       <c r="B101" s="7" t="n"/>
       <c r="C101" s="7" t="n"/>
       <c r="D101" s="6" t="n"/>
-      <c r="E101" s="8" t="n"/>
-      <c r="F101" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G101" s="6" t="inlineStr">
+      <c r="E101" s="6" t="n"/>
+      <c r="F101" s="8" t="n"/>
+      <c r="G101" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H101" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2157,11 +2219,12 @@
       <c r="B102" s="7" t="n"/>
       <c r="C102" s="7" t="n"/>
       <c r="D102" s="6" t="n"/>
-      <c r="E102" s="8" t="n"/>
-      <c r="F102" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G102" s="6" t="inlineStr">
+      <c r="E102" s="6" t="n"/>
+      <c r="F102" s="8" t="n"/>
+      <c r="G102" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H102" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2172,11 +2235,12 @@
       <c r="B103" s="7" t="n"/>
       <c r="C103" s="7" t="n"/>
       <c r="D103" s="6" t="n"/>
-      <c r="E103" s="8" t="n"/>
-      <c r="F103" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G103" s="6" t="inlineStr">
+      <c r="E103" s="6" t="n"/>
+      <c r="F103" s="8" t="n"/>
+      <c r="G103" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H103" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2187,11 +2251,12 @@
       <c r="B104" s="7" t="n"/>
       <c r="C104" s="7" t="n"/>
       <c r="D104" s="6" t="n"/>
-      <c r="E104" s="8" t="n"/>
-      <c r="F104" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G104" s="6" t="inlineStr">
+      <c r="E104" s="6" t="n"/>
+      <c r="F104" s="8" t="n"/>
+      <c r="G104" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H104" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2199,19 +2264,19 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="G5:G104" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Digite SIM ou NÃO" type="list">
+    <dataValidation sqref="H5:H104" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Digite SIM ou NÃO" type="list">
       <formula1>"SIM,NÃO"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5:F104" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Horas inválidas" error="Digite entre 1 e 24" type="decimal" operator="between">
+    <dataValidation sqref="G5:G104" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Horas inválidas" error="Entre 1 e 24" type="decimal" operator="between">
       <formula1>1</formula1>
       <formula2>24</formula2>
     </dataValidation>
-    <dataValidation sqref="E5:E104" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Custo inválido" error="Digite um valor &gt;= 0" type="decimal" operator="greaterThanOrEqual">
-      <formula1>0</formula1>
+    <dataValidation sqref="E5:E104" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Engenharia Elétrica,Engenharia de Software,Engenharia de Automação,Projetos,Montagem de Painel,Montagem de Campo,Comissionamento,Manutenção,Administrativo,Suporte Técnico"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2224,245 +2289,149 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>Cargos / Funções Sugeridos</t>
+          <t>Setores de Trabalho Disponíveis</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Cargo / Função</t>
+          <t>Setor de Trabalho</t>
         </is>
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>Área</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+          <t>Descrição</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>Engenheiro Eletricista</t>
+          <t>Engenharia Elétrica</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Engenharia</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>Projetos e especificações elétricas, dimensionamentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Engenheiro de Automação</t>
+          <t>Engenharia de Software</t>
         </is>
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>Engenharia</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
+          <t>Desenvolvimento de sistemas, SCADA, interfaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>Técnico em Automação</t>
+          <t>Engenharia de Automação</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Técnico</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+          <t>CLPs, redes industriais, programação de automação</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Técnico Eletrotécnico</t>
+          <t>Projetos</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>Técnico</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
+          <t>Documentação técnica, desenhos, diagramas</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>Técnico de Campo</t>
+          <t>Montagem de Painel</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Técnico</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
+          <t>Montagem física de painéis elétricos e CCMs</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>Eletricista Industrial</t>
+          <t>Montagem de Campo</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>Execução</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>Instalação elétrica em campo, cabeamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>Eletricista Instalador</t>
+          <t>Comissionamento</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Execução</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
+          <t>Testes, start-up e comissionamento de sistemas</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>Auxiliar Elétrico</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>Execução</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
+          <t>Manutenção preventiva e corretiva</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>Programador CLP</t>
+          <t>Suporte Técnico</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Automação</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
+          <t>Suporte remoto e presencial pós-obra</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>Programador SCADA</t>
+          <t>Administrativo</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>Automação</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>Projetista Elétrico</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>Projetos</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>Desenhista CAD</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>Projetos</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>Supervisor de Obras</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>Gestão</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>Encarregado de Obras</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>Gestão</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>Assistente Técnico</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>Suporte</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>Operador de Painel</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>Operação</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>Gerente de Projetos</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>Gestão</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>Coordenador de Automação</t>
-        </is>
-      </c>
-      <c r="B20" s="14" t="inlineStr">
-        <is>
-          <t>Gestão</t>
+          <t>Gestão administrativa, compras, logística</t>
         </is>
       </c>
     </row>
@@ -2480,165 +2449,228 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="85" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
-        <is>
-          <t>INSTRUÇÕES DE PREENCHIMENTO</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="6" customHeight="1">
-      <c r="A2" s="16" t="inlineStr"/>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="17" t="inlineStr">
-        <is>
-          <t>CAMPOS OBRIGATÓRIOS (fundo rosa)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Nome Completo: Nome completo do funcionário.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Cargo / Função: Função que o funcionário exerce na empresa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Custo por Hora (R$): Valor em reais por hora trabalhada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Horas por Dia Útil: Padrão = 9h. Aceita valores entre 1 e 24.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Ativo (SIM/NÃO): SIM = funcionário ativo, NÃO = inativo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="6" customHeight="1">
-      <c r="A9" s="16" t="inlineStr"/>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>CAMPOS OPCIONAIS (fundo azul)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • E-mail: E-mail profissional do funcionário.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Telefone: Formato sugerido: (37) 99999-9999</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="6" customHeight="1">
-      <c r="A13" s="16" t="inlineStr"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="20" t="inlineStr">
-        <is>
-          <t>COMO IMPORTAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. Preencha os dados a partir da linha 5 (não altere as linhas 1–4).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2. Salve no formato .xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  3. No sistema → Funcionários → botão 'Importar Excel'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4. Revise a pré-visualização e confirme a importação.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="6" customHeight="1">
-      <c r="A19" s="16" t="inlineStr"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="21" t="inlineStr">
-        <is>
-          <t>OBSERVAÇÕES</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Não altere os cabeçalhos (linha 3) nem a estrutura das colunas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • A linha verde (linha 4) é apenas exemplo — não será importada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Máximo de 100 funcionários por importação.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Consulte a aba 'Cargos de Referência' para sugestões de função.</t>
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Cargos / Funções Sugeridos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Cargo / Função</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>Setor Típico</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Engenheiro Eletricista</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>Engenharia Elétrica</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Engenheiro de Automação</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Engenharia de Automação</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Técnico em Automação</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Engenharia de Automação</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Programador CLP</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Engenharia de Automação</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Programador SCADA</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Engenharia de Software</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Projetista Elétrico</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Projetos</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Eletricista Industrial</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Montagem de Campo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Eletricista Instalador</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Montagem de Campo</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Auxiliar Elétrico</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Montagem de Campo</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Montador de Painel</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Montagem de Painel</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Técnico de Campo</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Montagem de Campo</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Supervisor de Obras</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Montagem de Campo</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Encarregado de Obras</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Montagem de Campo</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Assistente Técnico</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>Suporte Técnico</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Gerente de Projetos</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Administrativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Coordenador de Automação</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Engenharia de Automação</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/template_funcionarios.xlsx
+++ b/docs/template_funcionarios.xlsx
@@ -8,8 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Funcionários" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Valores Válidos" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="💡 Calculadora Salário" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="💡 Calculadora CLT vs PJ" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -73,7 +72,12 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -81,8 +85,18 @@
       <color rgb="00166534"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00333333"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001e40af"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -126,17 +140,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4F7FB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="000284C7"/>
+        <fgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
   </fills>
@@ -166,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -204,18 +208,17 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -581,18 +584,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I206"/>
+  <dimension ref="A1:J206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -605,14 +609,14 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>🔴 Obrigatório   |   🔵 Opcional   |   🟢 Calculado automaticamente (Custo/h = Salário Mensal ÷ 220)   |   🟡 Exemplo</t>
+          <t>🔴 Obrigatório   |   🔵 Opcional   |   CLT = 220h/mês   |   PJ = 176h/mês   |   Custo/hora é calculado automaticamente pelo tipo de contrato</t>
         </is>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>💡  Preencha o SALÁRIO MENSAL (R$) — o sistema calculará o Custo/Hora automaticamente (÷ 220h/mês). Se preferir, preencha o Custo/Hora diretamente e deixe o salário em branco.</t>
+          <t>💡  CLT: custo/hora = salário ÷ 220h   |   PJ: custo/hora = valor ÷ 176h   |   Se preencher o Salário Mensal, o Custo/Hora é calculado automaticamente.</t>
         </is>
       </c>
     </row>
@@ -644,20 +648,25 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
+          <t>Contrato * (CLT/PJ)</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
           <t>Salário Mensal (R$)</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Custo por Hora (R$) *</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Horas por Dia Útil *</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>Ativo (SIM/NÃO) *</t>
         </is>
@@ -689,16 +698,21 @@
           <t>Montagem de Campo</t>
         </is>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="n">
         <v>3960</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="H5" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="H5" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -707,7 +721,7 @@
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>↑ EXEMPLO: Salário R$3.960/mês ÷ 220h = R$18,00/hora.  Apague esta linha e a linha acima antes de importar, ou deixe — o sistema as ignora automaticamente.</t>
+          <t>↑ EXEMPLO: CLT — Salário R$3.960/mês ÷ 220h = R$18,00/hora  |  PJ: Salário R$5.280/mês ÷ 176h = R$30,00/hora</t>
         </is>
       </c>
     </row>
@@ -717,12 +731,17 @@
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="8" t="n"/>
       <c r="E7" s="8" t="n"/>
-      <c r="F7" s="10" t="n"/>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="11" t="n"/>
+      <c r="I7" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -734,12 +753,17 @@
       <c r="C8" s="9" t="n"/>
       <c r="D8" s="8" t="n"/>
       <c r="E8" s="8" t="n"/>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="n"/>
+      <c r="H8" s="11" t="n"/>
+      <c r="I8" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -751,12 +775,17 @@
       <c r="C9" s="9" t="n"/>
       <c r="D9" s="8" t="n"/>
       <c r="E9" s="8" t="n"/>
-      <c r="F9" s="10" t="n"/>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="11" t="n"/>
+      <c r="I9" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -768,12 +797,17 @@
       <c r="C10" s="9" t="n"/>
       <c r="D10" s="8" t="n"/>
       <c r="E10" s="8" t="n"/>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="11" t="n"/>
-      <c r="H10" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="11" t="n"/>
+      <c r="I10" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -785,12 +819,17 @@
       <c r="C11" s="9" t="n"/>
       <c r="D11" s="8" t="n"/>
       <c r="E11" s="8" t="n"/>
-      <c r="F11" s="10" t="n"/>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="n"/>
+      <c r="H11" s="11" t="n"/>
+      <c r="I11" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -802,12 +841,17 @@
       <c r="C12" s="9" t="n"/>
       <c r="D12" s="8" t="n"/>
       <c r="E12" s="8" t="n"/>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="n"/>
+      <c r="H12" s="11" t="n"/>
+      <c r="I12" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -819,12 +863,17 @@
       <c r="C13" s="9" t="n"/>
       <c r="D13" s="8" t="n"/>
       <c r="E13" s="8" t="n"/>
-      <c r="F13" s="10" t="n"/>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I13" s="8" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="11" t="n"/>
+      <c r="I13" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -836,12 +885,17 @@
       <c r="C14" s="9" t="n"/>
       <c r="D14" s="8" t="n"/>
       <c r="E14" s="8" t="n"/>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="11" t="n"/>
-      <c r="H14" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="n"/>
+      <c r="H14" s="11" t="n"/>
+      <c r="I14" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -853,12 +907,17 @@
       <c r="C15" s="9" t="n"/>
       <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="n"/>
-      <c r="F15" s="10" t="n"/>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I15" s="8" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="n"/>
+      <c r="H15" s="11" t="n"/>
+      <c r="I15" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -870,12 +929,17 @@
       <c r="C16" s="9" t="n"/>
       <c r="D16" s="8" t="n"/>
       <c r="E16" s="8" t="n"/>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="11" t="n"/>
-      <c r="H16" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="n"/>
+      <c r="H16" s="11" t="n"/>
+      <c r="I16" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -887,12 +951,17 @@
       <c r="C17" s="9" t="n"/>
       <c r="D17" s="8" t="n"/>
       <c r="E17" s="8" t="n"/>
-      <c r="F17" s="10" t="n"/>
-      <c r="G17" s="11" t="n"/>
-      <c r="H17" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I17" s="8" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="n"/>
+      <c r="H17" s="11" t="n"/>
+      <c r="I17" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -904,12 +973,17 @@
       <c r="C18" s="9" t="n"/>
       <c r="D18" s="8" t="n"/>
       <c r="E18" s="8" t="n"/>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="11" t="n"/>
-      <c r="H18" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="n"/>
+      <c r="H18" s="11" t="n"/>
+      <c r="I18" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -921,12 +995,17 @@
       <c r="C19" s="9" t="n"/>
       <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="n"/>
-      <c r="F19" s="10" t="n"/>
-      <c r="G19" s="11" t="n"/>
-      <c r="H19" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="n"/>
+      <c r="H19" s="11" t="n"/>
+      <c r="I19" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -938,12 +1017,17 @@
       <c r="C20" s="9" t="n"/>
       <c r="D20" s="8" t="n"/>
       <c r="E20" s="8" t="n"/>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="11" t="n"/>
-      <c r="H20" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="n"/>
+      <c r="H20" s="11" t="n"/>
+      <c r="I20" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -955,12 +1039,17 @@
       <c r="C21" s="9" t="n"/>
       <c r="D21" s="8" t="n"/>
       <c r="E21" s="8" t="n"/>
-      <c r="F21" s="10" t="n"/>
-      <c r="G21" s="11" t="n"/>
-      <c r="H21" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="n"/>
+      <c r="H21" s="11" t="n"/>
+      <c r="I21" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -972,12 +1061,17 @@
       <c r="C22" s="9" t="n"/>
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="11" t="n"/>
-      <c r="H22" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="n"/>
+      <c r="H22" s="11" t="n"/>
+      <c r="I22" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -989,12 +1083,17 @@
       <c r="C23" s="9" t="n"/>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="n"/>
-      <c r="F23" s="10" t="n"/>
-      <c r="G23" s="11" t="n"/>
-      <c r="H23" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I23" s="8" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="n"/>
+      <c r="H23" s="11" t="n"/>
+      <c r="I23" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1006,12 +1105,17 @@
       <c r="C24" s="9" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
-      <c r="F24" s="10" t="n"/>
-      <c r="G24" s="11" t="n"/>
-      <c r="H24" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="n"/>
+      <c r="H24" s="11" t="n"/>
+      <c r="I24" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1023,12 +1127,17 @@
       <c r="C25" s="9" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="n"/>
-      <c r="F25" s="10" t="n"/>
-      <c r="G25" s="11" t="n"/>
-      <c r="H25" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I25" s="8" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="n"/>
+      <c r="H25" s="11" t="n"/>
+      <c r="I25" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1040,12 +1149,17 @@
       <c r="C26" s="9" t="n"/>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
-      <c r="F26" s="10" t="n"/>
-      <c r="G26" s="11" t="n"/>
-      <c r="H26" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I26" s="8" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="n"/>
+      <c r="H26" s="11" t="n"/>
+      <c r="I26" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1057,12 +1171,17 @@
       <c r="C27" s="9" t="n"/>
       <c r="D27" s="8" t="n"/>
       <c r="E27" s="8" t="n"/>
-      <c r="F27" s="10" t="n"/>
-      <c r="G27" s="11" t="n"/>
-      <c r="H27" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I27" s="8" t="inlineStr">
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="n"/>
+      <c r="H27" s="11" t="n"/>
+      <c r="I27" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J27" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1074,12 +1193,17 @@
       <c r="C28" s="9" t="n"/>
       <c r="D28" s="8" t="n"/>
       <c r="E28" s="8" t="n"/>
-      <c r="F28" s="10" t="n"/>
-      <c r="G28" s="11" t="n"/>
-      <c r="H28" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I28" s="8" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="n"/>
+      <c r="H28" s="11" t="n"/>
+      <c r="I28" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J28" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1091,12 +1215,17 @@
       <c r="C29" s="9" t="n"/>
       <c r="D29" s="8" t="n"/>
       <c r="E29" s="8" t="n"/>
-      <c r="F29" s="10" t="n"/>
-      <c r="G29" s="11" t="n"/>
-      <c r="H29" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I29" s="8" t="inlineStr">
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="n"/>
+      <c r="H29" s="11" t="n"/>
+      <c r="I29" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J29" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1108,12 +1237,17 @@
       <c r="C30" s="9" t="n"/>
       <c r="D30" s="8" t="n"/>
       <c r="E30" s="8" t="n"/>
-      <c r="F30" s="10" t="n"/>
-      <c r="G30" s="11" t="n"/>
-      <c r="H30" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I30" s="8" t="inlineStr">
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="n"/>
+      <c r="H30" s="11" t="n"/>
+      <c r="I30" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J30" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1125,12 +1259,17 @@
       <c r="C31" s="9" t="n"/>
       <c r="D31" s="8" t="n"/>
       <c r="E31" s="8" t="n"/>
-      <c r="F31" s="10" t="n"/>
-      <c r="G31" s="11" t="n"/>
-      <c r="H31" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="n"/>
+      <c r="H31" s="11" t="n"/>
+      <c r="I31" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J31" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1142,12 +1281,17 @@
       <c r="C32" s="9" t="n"/>
       <c r="D32" s="8" t="n"/>
       <c r="E32" s="8" t="n"/>
-      <c r="F32" s="10" t="n"/>
-      <c r="G32" s="11" t="n"/>
-      <c r="H32" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I32" s="8" t="inlineStr">
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="n"/>
+      <c r="H32" s="11" t="n"/>
+      <c r="I32" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J32" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1159,12 +1303,17 @@
       <c r="C33" s="9" t="n"/>
       <c r="D33" s="8" t="n"/>
       <c r="E33" s="8" t="n"/>
-      <c r="F33" s="10" t="n"/>
-      <c r="G33" s="11" t="n"/>
-      <c r="H33" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I33" s="8" t="inlineStr">
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="n"/>
+      <c r="H33" s="11" t="n"/>
+      <c r="I33" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J33" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1176,12 +1325,17 @@
       <c r="C34" s="9" t="n"/>
       <c r="D34" s="8" t="n"/>
       <c r="E34" s="8" t="n"/>
-      <c r="F34" s="10" t="n"/>
-      <c r="G34" s="11" t="n"/>
-      <c r="H34" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I34" s="8" t="inlineStr">
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="n"/>
+      <c r="H34" s="11" t="n"/>
+      <c r="I34" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J34" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1193,12 +1347,17 @@
       <c r="C35" s="9" t="n"/>
       <c r="D35" s="8" t="n"/>
       <c r="E35" s="8" t="n"/>
-      <c r="F35" s="10" t="n"/>
-      <c r="G35" s="11" t="n"/>
-      <c r="H35" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I35" s="8" t="inlineStr">
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="n"/>
+      <c r="H35" s="11" t="n"/>
+      <c r="I35" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J35" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1210,12 +1369,17 @@
       <c r="C36" s="9" t="n"/>
       <c r="D36" s="8" t="n"/>
       <c r="E36" s="8" t="n"/>
-      <c r="F36" s="10" t="n"/>
-      <c r="G36" s="11" t="n"/>
-      <c r="H36" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I36" s="8" t="inlineStr">
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="n"/>
+      <c r="H36" s="11" t="n"/>
+      <c r="I36" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J36" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1227,12 +1391,17 @@
       <c r="C37" s="9" t="n"/>
       <c r="D37" s="8" t="n"/>
       <c r="E37" s="8" t="n"/>
-      <c r="F37" s="10" t="n"/>
-      <c r="G37" s="11" t="n"/>
-      <c r="H37" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I37" s="8" t="inlineStr">
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G37" s="10" t="n"/>
+      <c r="H37" s="11" t="n"/>
+      <c r="I37" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J37" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1244,12 +1413,17 @@
       <c r="C38" s="9" t="n"/>
       <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
-      <c r="F38" s="10" t="n"/>
-      <c r="G38" s="11" t="n"/>
-      <c r="H38" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I38" s="8" t="inlineStr">
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G38" s="10" t="n"/>
+      <c r="H38" s="11" t="n"/>
+      <c r="I38" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J38" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1261,12 +1435,17 @@
       <c r="C39" s="9" t="n"/>
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="n"/>
-      <c r="F39" s="10" t="n"/>
-      <c r="G39" s="11" t="n"/>
-      <c r="H39" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I39" s="8" t="inlineStr">
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G39" s="10" t="n"/>
+      <c r="H39" s="11" t="n"/>
+      <c r="I39" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J39" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1278,12 +1457,17 @@
       <c r="C40" s="9" t="n"/>
       <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="n"/>
-      <c r="F40" s="10" t="n"/>
-      <c r="G40" s="11" t="n"/>
-      <c r="H40" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I40" s="8" t="inlineStr">
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="n"/>
+      <c r="H40" s="11" t="n"/>
+      <c r="I40" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J40" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1295,12 +1479,17 @@
       <c r="C41" s="9" t="n"/>
       <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="n"/>
-      <c r="F41" s="10" t="n"/>
-      <c r="G41" s="11" t="n"/>
-      <c r="H41" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I41" s="8" t="inlineStr">
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G41" s="10" t="n"/>
+      <c r="H41" s="11" t="n"/>
+      <c r="I41" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J41" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1312,12 +1501,17 @@
       <c r="C42" s="9" t="n"/>
       <c r="D42" s="8" t="n"/>
       <c r="E42" s="8" t="n"/>
-      <c r="F42" s="10" t="n"/>
-      <c r="G42" s="11" t="n"/>
-      <c r="H42" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I42" s="8" t="inlineStr">
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="n"/>
+      <c r="H42" s="11" t="n"/>
+      <c r="I42" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J42" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1329,12 +1523,17 @@
       <c r="C43" s="9" t="n"/>
       <c r="D43" s="8" t="n"/>
       <c r="E43" s="8" t="n"/>
-      <c r="F43" s="10" t="n"/>
-      <c r="G43" s="11" t="n"/>
-      <c r="H43" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I43" s="8" t="inlineStr">
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G43" s="10" t="n"/>
+      <c r="H43" s="11" t="n"/>
+      <c r="I43" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J43" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1346,12 +1545,17 @@
       <c r="C44" s="9" t="n"/>
       <c r="D44" s="8" t="n"/>
       <c r="E44" s="8" t="n"/>
-      <c r="F44" s="10" t="n"/>
-      <c r="G44" s="11" t="n"/>
-      <c r="H44" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I44" s="8" t="inlineStr">
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G44" s="10" t="n"/>
+      <c r="H44" s="11" t="n"/>
+      <c r="I44" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J44" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1363,12 +1567,17 @@
       <c r="C45" s="9" t="n"/>
       <c r="D45" s="8" t="n"/>
       <c r="E45" s="8" t="n"/>
-      <c r="F45" s="10" t="n"/>
-      <c r="G45" s="11" t="n"/>
-      <c r="H45" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I45" s="8" t="inlineStr">
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G45" s="10" t="n"/>
+      <c r="H45" s="11" t="n"/>
+      <c r="I45" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J45" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1380,12 +1589,17 @@
       <c r="C46" s="9" t="n"/>
       <c r="D46" s="8" t="n"/>
       <c r="E46" s="8" t="n"/>
-      <c r="F46" s="10" t="n"/>
-      <c r="G46" s="11" t="n"/>
-      <c r="H46" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I46" s="8" t="inlineStr">
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G46" s="10" t="n"/>
+      <c r="H46" s="11" t="n"/>
+      <c r="I46" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J46" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1397,12 +1611,17 @@
       <c r="C47" s="9" t="n"/>
       <c r="D47" s="8" t="n"/>
       <c r="E47" s="8" t="n"/>
-      <c r="F47" s="10" t="n"/>
-      <c r="G47" s="11" t="n"/>
-      <c r="H47" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I47" s="8" t="inlineStr">
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G47" s="10" t="n"/>
+      <c r="H47" s="11" t="n"/>
+      <c r="I47" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J47" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1414,12 +1633,17 @@
       <c r="C48" s="9" t="n"/>
       <c r="D48" s="8" t="n"/>
       <c r="E48" s="8" t="n"/>
-      <c r="F48" s="10" t="n"/>
-      <c r="G48" s="11" t="n"/>
-      <c r="H48" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I48" s="8" t="inlineStr">
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G48" s="10" t="n"/>
+      <c r="H48" s="11" t="n"/>
+      <c r="I48" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J48" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1431,12 +1655,17 @@
       <c r="C49" s="9" t="n"/>
       <c r="D49" s="8" t="n"/>
       <c r="E49" s="8" t="n"/>
-      <c r="F49" s="10" t="n"/>
-      <c r="G49" s="11" t="n"/>
-      <c r="H49" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I49" s="8" t="inlineStr">
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G49" s="10" t="n"/>
+      <c r="H49" s="11" t="n"/>
+      <c r="I49" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J49" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1448,12 +1677,17 @@
       <c r="C50" s="9" t="n"/>
       <c r="D50" s="8" t="n"/>
       <c r="E50" s="8" t="n"/>
-      <c r="F50" s="10" t="n"/>
-      <c r="G50" s="11" t="n"/>
-      <c r="H50" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I50" s="8" t="inlineStr">
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G50" s="10" t="n"/>
+      <c r="H50" s="11" t="n"/>
+      <c r="I50" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J50" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1465,12 +1699,17 @@
       <c r="C51" s="9" t="n"/>
       <c r="D51" s="8" t="n"/>
       <c r="E51" s="8" t="n"/>
-      <c r="F51" s="10" t="n"/>
-      <c r="G51" s="11" t="n"/>
-      <c r="H51" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I51" s="8" t="inlineStr">
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G51" s="10" t="n"/>
+      <c r="H51" s="11" t="n"/>
+      <c r="I51" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J51" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1482,12 +1721,17 @@
       <c r="C52" s="9" t="n"/>
       <c r="D52" s="8" t="n"/>
       <c r="E52" s="8" t="n"/>
-      <c r="F52" s="10" t="n"/>
-      <c r="G52" s="11" t="n"/>
-      <c r="H52" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I52" s="8" t="inlineStr">
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G52" s="10" t="n"/>
+      <c r="H52" s="11" t="n"/>
+      <c r="I52" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J52" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1499,12 +1743,17 @@
       <c r="C53" s="9" t="n"/>
       <c r="D53" s="8" t="n"/>
       <c r="E53" s="8" t="n"/>
-      <c r="F53" s="10" t="n"/>
-      <c r="G53" s="11" t="n"/>
-      <c r="H53" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I53" s="8" t="inlineStr">
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G53" s="10" t="n"/>
+      <c r="H53" s="11" t="n"/>
+      <c r="I53" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J53" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1516,12 +1765,17 @@
       <c r="C54" s="9" t="n"/>
       <c r="D54" s="8" t="n"/>
       <c r="E54" s="8" t="n"/>
-      <c r="F54" s="10" t="n"/>
-      <c r="G54" s="11" t="n"/>
-      <c r="H54" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I54" s="8" t="inlineStr">
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G54" s="10" t="n"/>
+      <c r="H54" s="11" t="n"/>
+      <c r="I54" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J54" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1533,12 +1787,17 @@
       <c r="C55" s="9" t="n"/>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="n"/>
-      <c r="F55" s="10" t="n"/>
-      <c r="G55" s="11" t="n"/>
-      <c r="H55" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I55" s="8" t="inlineStr">
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G55" s="10" t="n"/>
+      <c r="H55" s="11" t="n"/>
+      <c r="I55" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J55" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1550,12 +1809,17 @@
       <c r="C56" s="9" t="n"/>
       <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
-      <c r="F56" s="10" t="n"/>
-      <c r="G56" s="11" t="n"/>
-      <c r="H56" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I56" s="8" t="inlineStr">
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G56" s="10" t="n"/>
+      <c r="H56" s="11" t="n"/>
+      <c r="I56" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J56" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1567,12 +1831,17 @@
       <c r="C57" s="9" t="n"/>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
-      <c r="F57" s="10" t="n"/>
-      <c r="G57" s="11" t="n"/>
-      <c r="H57" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I57" s="8" t="inlineStr">
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G57" s="10" t="n"/>
+      <c r="H57" s="11" t="n"/>
+      <c r="I57" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J57" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1584,12 +1853,17 @@
       <c r="C58" s="9" t="n"/>
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="n"/>
-      <c r="F58" s="10" t="n"/>
-      <c r="G58" s="11" t="n"/>
-      <c r="H58" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I58" s="8" t="inlineStr">
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G58" s="10" t="n"/>
+      <c r="H58" s="11" t="n"/>
+      <c r="I58" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J58" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1601,12 +1875,17 @@
       <c r="C59" s="9" t="n"/>
       <c r="D59" s="8" t="n"/>
       <c r="E59" s="8" t="n"/>
-      <c r="F59" s="10" t="n"/>
-      <c r="G59" s="11" t="n"/>
-      <c r="H59" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I59" s="8" t="inlineStr">
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G59" s="10" t="n"/>
+      <c r="H59" s="11" t="n"/>
+      <c r="I59" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J59" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1618,12 +1897,17 @@
       <c r="C60" s="9" t="n"/>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="n"/>
-      <c r="F60" s="10" t="n"/>
-      <c r="G60" s="11" t="n"/>
-      <c r="H60" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I60" s="8" t="inlineStr">
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G60" s="10" t="n"/>
+      <c r="H60" s="11" t="n"/>
+      <c r="I60" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J60" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1635,12 +1919,17 @@
       <c r="C61" s="9" t="n"/>
       <c r="D61" s="8" t="n"/>
       <c r="E61" s="8" t="n"/>
-      <c r="F61" s="10" t="n"/>
-      <c r="G61" s="11" t="n"/>
-      <c r="H61" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I61" s="8" t="inlineStr">
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G61" s="10" t="n"/>
+      <c r="H61" s="11" t="n"/>
+      <c r="I61" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J61" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1652,12 +1941,17 @@
       <c r="C62" s="9" t="n"/>
       <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
-      <c r="F62" s="10" t="n"/>
-      <c r="G62" s="11" t="n"/>
-      <c r="H62" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I62" s="8" t="inlineStr">
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G62" s="10" t="n"/>
+      <c r="H62" s="11" t="n"/>
+      <c r="I62" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J62" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1669,12 +1963,17 @@
       <c r="C63" s="9" t="n"/>
       <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
-      <c r="F63" s="10" t="n"/>
-      <c r="G63" s="11" t="n"/>
-      <c r="H63" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I63" s="8" t="inlineStr">
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G63" s="10" t="n"/>
+      <c r="H63" s="11" t="n"/>
+      <c r="I63" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J63" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1686,12 +1985,17 @@
       <c r="C64" s="9" t="n"/>
       <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="n"/>
-      <c r="F64" s="10" t="n"/>
-      <c r="G64" s="11" t="n"/>
-      <c r="H64" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I64" s="8" t="inlineStr">
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G64" s="10" t="n"/>
+      <c r="H64" s="11" t="n"/>
+      <c r="I64" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J64" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1703,12 +2007,17 @@
       <c r="C65" s="9" t="n"/>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="n"/>
-      <c r="F65" s="10" t="n"/>
-      <c r="G65" s="11" t="n"/>
-      <c r="H65" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I65" s="8" t="inlineStr">
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G65" s="10" t="n"/>
+      <c r="H65" s="11" t="n"/>
+      <c r="I65" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J65" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1720,12 +2029,17 @@
       <c r="C66" s="9" t="n"/>
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="n"/>
-      <c r="F66" s="10" t="n"/>
-      <c r="G66" s="11" t="n"/>
-      <c r="H66" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I66" s="8" t="inlineStr">
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G66" s="10" t="n"/>
+      <c r="H66" s="11" t="n"/>
+      <c r="I66" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J66" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1737,12 +2051,17 @@
       <c r="C67" s="9" t="n"/>
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
-      <c r="F67" s="10" t="n"/>
-      <c r="G67" s="11" t="n"/>
-      <c r="H67" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I67" s="8" t="inlineStr">
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G67" s="10" t="n"/>
+      <c r="H67" s="11" t="n"/>
+      <c r="I67" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J67" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1754,12 +2073,17 @@
       <c r="C68" s="9" t="n"/>
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
-      <c r="F68" s="10" t="n"/>
-      <c r="G68" s="11" t="n"/>
-      <c r="H68" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I68" s="8" t="inlineStr">
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G68" s="10" t="n"/>
+      <c r="H68" s="11" t="n"/>
+      <c r="I68" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J68" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1771,12 +2095,17 @@
       <c r="C69" s="9" t="n"/>
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="n"/>
-      <c r="F69" s="10" t="n"/>
-      <c r="G69" s="11" t="n"/>
-      <c r="H69" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I69" s="8" t="inlineStr">
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G69" s="10" t="n"/>
+      <c r="H69" s="11" t="n"/>
+      <c r="I69" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J69" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1788,12 +2117,17 @@
       <c r="C70" s="9" t="n"/>
       <c r="D70" s="8" t="n"/>
       <c r="E70" s="8" t="n"/>
-      <c r="F70" s="10" t="n"/>
-      <c r="G70" s="11" t="n"/>
-      <c r="H70" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I70" s="8" t="inlineStr">
+      <c r="F70" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G70" s="10" t="n"/>
+      <c r="H70" s="11" t="n"/>
+      <c r="I70" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J70" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1805,12 +2139,17 @@
       <c r="C71" s="9" t="n"/>
       <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
-      <c r="F71" s="10" t="n"/>
-      <c r="G71" s="11" t="n"/>
-      <c r="H71" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I71" s="8" t="inlineStr">
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G71" s="10" t="n"/>
+      <c r="H71" s="11" t="n"/>
+      <c r="I71" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J71" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1822,12 +2161,17 @@
       <c r="C72" s="9" t="n"/>
       <c r="D72" s="8" t="n"/>
       <c r="E72" s="8" t="n"/>
-      <c r="F72" s="10" t="n"/>
-      <c r="G72" s="11" t="n"/>
-      <c r="H72" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I72" s="8" t="inlineStr">
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G72" s="10" t="n"/>
+      <c r="H72" s="11" t="n"/>
+      <c r="I72" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J72" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1839,12 +2183,17 @@
       <c r="C73" s="9" t="n"/>
       <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
-      <c r="F73" s="10" t="n"/>
-      <c r="G73" s="11" t="n"/>
-      <c r="H73" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I73" s="8" t="inlineStr">
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G73" s="10" t="n"/>
+      <c r="H73" s="11" t="n"/>
+      <c r="I73" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J73" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1856,12 +2205,17 @@
       <c r="C74" s="9" t="n"/>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
-      <c r="F74" s="10" t="n"/>
-      <c r="G74" s="11" t="n"/>
-      <c r="H74" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I74" s="8" t="inlineStr">
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G74" s="10" t="n"/>
+      <c r="H74" s="11" t="n"/>
+      <c r="I74" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J74" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1873,12 +2227,17 @@
       <c r="C75" s="9" t="n"/>
       <c r="D75" s="8" t="n"/>
       <c r="E75" s="8" t="n"/>
-      <c r="F75" s="10" t="n"/>
-      <c r="G75" s="11" t="n"/>
-      <c r="H75" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I75" s="8" t="inlineStr">
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G75" s="10" t="n"/>
+      <c r="H75" s="11" t="n"/>
+      <c r="I75" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J75" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1890,12 +2249,17 @@
       <c r="C76" s="9" t="n"/>
       <c r="D76" s="8" t="n"/>
       <c r="E76" s="8" t="n"/>
-      <c r="F76" s="10" t="n"/>
-      <c r="G76" s="11" t="n"/>
-      <c r="H76" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I76" s="8" t="inlineStr">
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G76" s="10" t="n"/>
+      <c r="H76" s="11" t="n"/>
+      <c r="I76" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J76" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1907,12 +2271,17 @@
       <c r="C77" s="9" t="n"/>
       <c r="D77" s="8" t="n"/>
       <c r="E77" s="8" t="n"/>
-      <c r="F77" s="10" t="n"/>
-      <c r="G77" s="11" t="n"/>
-      <c r="H77" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I77" s="8" t="inlineStr">
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G77" s="10" t="n"/>
+      <c r="H77" s="11" t="n"/>
+      <c r="I77" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J77" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1924,12 +2293,17 @@
       <c r="C78" s="9" t="n"/>
       <c r="D78" s="8" t="n"/>
       <c r="E78" s="8" t="n"/>
-      <c r="F78" s="10" t="n"/>
-      <c r="G78" s="11" t="n"/>
-      <c r="H78" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I78" s="8" t="inlineStr">
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G78" s="10" t="n"/>
+      <c r="H78" s="11" t="n"/>
+      <c r="I78" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J78" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1941,12 +2315,17 @@
       <c r="C79" s="9" t="n"/>
       <c r="D79" s="8" t="n"/>
       <c r="E79" s="8" t="n"/>
-      <c r="F79" s="10" t="n"/>
-      <c r="G79" s="11" t="n"/>
-      <c r="H79" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I79" s="8" t="inlineStr">
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G79" s="10" t="n"/>
+      <c r="H79" s="11" t="n"/>
+      <c r="I79" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J79" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1958,12 +2337,17 @@
       <c r="C80" s="9" t="n"/>
       <c r="D80" s="8" t="n"/>
       <c r="E80" s="8" t="n"/>
-      <c r="F80" s="10" t="n"/>
-      <c r="G80" s="11" t="n"/>
-      <c r="H80" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I80" s="8" t="inlineStr">
+      <c r="F80" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G80" s="10" t="n"/>
+      <c r="H80" s="11" t="n"/>
+      <c r="I80" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J80" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1975,12 +2359,17 @@
       <c r="C81" s="9" t="n"/>
       <c r="D81" s="8" t="n"/>
       <c r="E81" s="8" t="n"/>
-      <c r="F81" s="10" t="n"/>
-      <c r="G81" s="11" t="n"/>
-      <c r="H81" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I81" s="8" t="inlineStr">
+      <c r="F81" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G81" s="10" t="n"/>
+      <c r="H81" s="11" t="n"/>
+      <c r="I81" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J81" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1992,12 +2381,17 @@
       <c r="C82" s="9" t="n"/>
       <c r="D82" s="8" t="n"/>
       <c r="E82" s="8" t="n"/>
-      <c r="F82" s="10" t="n"/>
-      <c r="G82" s="11" t="n"/>
-      <c r="H82" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I82" s="8" t="inlineStr">
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G82" s="10" t="n"/>
+      <c r="H82" s="11" t="n"/>
+      <c r="I82" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J82" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2009,12 +2403,17 @@
       <c r="C83" s="9" t="n"/>
       <c r="D83" s="8" t="n"/>
       <c r="E83" s="8" t="n"/>
-      <c r="F83" s="10" t="n"/>
-      <c r="G83" s="11" t="n"/>
-      <c r="H83" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I83" s="8" t="inlineStr">
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G83" s="10" t="n"/>
+      <c r="H83" s="11" t="n"/>
+      <c r="I83" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J83" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2026,12 +2425,17 @@
       <c r="C84" s="9" t="n"/>
       <c r="D84" s="8" t="n"/>
       <c r="E84" s="8" t="n"/>
-      <c r="F84" s="10" t="n"/>
-      <c r="G84" s="11" t="n"/>
-      <c r="H84" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I84" s="8" t="inlineStr">
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G84" s="10" t="n"/>
+      <c r="H84" s="11" t="n"/>
+      <c r="I84" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J84" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2043,12 +2447,17 @@
       <c r="C85" s="9" t="n"/>
       <c r="D85" s="8" t="n"/>
       <c r="E85" s="8" t="n"/>
-      <c r="F85" s="10" t="n"/>
-      <c r="G85" s="11" t="n"/>
-      <c r="H85" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I85" s="8" t="inlineStr">
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G85" s="10" t="n"/>
+      <c r="H85" s="11" t="n"/>
+      <c r="I85" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J85" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2060,12 +2469,17 @@
       <c r="C86" s="9" t="n"/>
       <c r="D86" s="8" t="n"/>
       <c r="E86" s="8" t="n"/>
-      <c r="F86" s="10" t="n"/>
-      <c r="G86" s="11" t="n"/>
-      <c r="H86" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I86" s="8" t="inlineStr">
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G86" s="10" t="n"/>
+      <c r="H86" s="11" t="n"/>
+      <c r="I86" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J86" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2077,12 +2491,17 @@
       <c r="C87" s="9" t="n"/>
       <c r="D87" s="8" t="n"/>
       <c r="E87" s="8" t="n"/>
-      <c r="F87" s="10" t="n"/>
-      <c r="G87" s="11" t="n"/>
-      <c r="H87" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I87" s="8" t="inlineStr">
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G87" s="10" t="n"/>
+      <c r="H87" s="11" t="n"/>
+      <c r="I87" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J87" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2094,12 +2513,17 @@
       <c r="C88" s="9" t="n"/>
       <c r="D88" s="8" t="n"/>
       <c r="E88" s="8" t="n"/>
-      <c r="F88" s="10" t="n"/>
-      <c r="G88" s="11" t="n"/>
-      <c r="H88" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I88" s="8" t="inlineStr">
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G88" s="10" t="n"/>
+      <c r="H88" s="11" t="n"/>
+      <c r="I88" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J88" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2111,12 +2535,17 @@
       <c r="C89" s="9" t="n"/>
       <c r="D89" s="8" t="n"/>
       <c r="E89" s="8" t="n"/>
-      <c r="F89" s="10" t="n"/>
-      <c r="G89" s="11" t="n"/>
-      <c r="H89" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I89" s="8" t="inlineStr">
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G89" s="10" t="n"/>
+      <c r="H89" s="11" t="n"/>
+      <c r="I89" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J89" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2128,12 +2557,17 @@
       <c r="C90" s="9" t="n"/>
       <c r="D90" s="8" t="n"/>
       <c r="E90" s="8" t="n"/>
-      <c r="F90" s="10" t="n"/>
-      <c r="G90" s="11" t="n"/>
-      <c r="H90" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I90" s="8" t="inlineStr">
+      <c r="F90" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G90" s="10" t="n"/>
+      <c r="H90" s="11" t="n"/>
+      <c r="I90" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J90" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2145,12 +2579,17 @@
       <c r="C91" s="9" t="n"/>
       <c r="D91" s="8" t="n"/>
       <c r="E91" s="8" t="n"/>
-      <c r="F91" s="10" t="n"/>
-      <c r="G91" s="11" t="n"/>
-      <c r="H91" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I91" s="8" t="inlineStr">
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G91" s="10" t="n"/>
+      <c r="H91" s="11" t="n"/>
+      <c r="I91" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J91" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2162,12 +2601,17 @@
       <c r="C92" s="9" t="n"/>
       <c r="D92" s="8" t="n"/>
       <c r="E92" s="8" t="n"/>
-      <c r="F92" s="10" t="n"/>
-      <c r="G92" s="11" t="n"/>
-      <c r="H92" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I92" s="8" t="inlineStr">
+      <c r="F92" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G92" s="10" t="n"/>
+      <c r="H92" s="11" t="n"/>
+      <c r="I92" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J92" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2179,12 +2623,17 @@
       <c r="C93" s="9" t="n"/>
       <c r="D93" s="8" t="n"/>
       <c r="E93" s="8" t="n"/>
-      <c r="F93" s="10" t="n"/>
-      <c r="G93" s="11" t="n"/>
-      <c r="H93" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I93" s="8" t="inlineStr">
+      <c r="F93" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G93" s="10" t="n"/>
+      <c r="H93" s="11" t="n"/>
+      <c r="I93" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J93" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2196,12 +2645,17 @@
       <c r="C94" s="9" t="n"/>
       <c r="D94" s="8" t="n"/>
       <c r="E94" s="8" t="n"/>
-      <c r="F94" s="10" t="n"/>
-      <c r="G94" s="11" t="n"/>
-      <c r="H94" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I94" s="8" t="inlineStr">
+      <c r="F94" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G94" s="10" t="n"/>
+      <c r="H94" s="11" t="n"/>
+      <c r="I94" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J94" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2213,12 +2667,17 @@
       <c r="C95" s="9" t="n"/>
       <c r="D95" s="8" t="n"/>
       <c r="E95" s="8" t="n"/>
-      <c r="F95" s="10" t="n"/>
-      <c r="G95" s="11" t="n"/>
-      <c r="H95" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I95" s="8" t="inlineStr">
+      <c r="F95" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G95" s="10" t="n"/>
+      <c r="H95" s="11" t="n"/>
+      <c r="I95" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J95" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2230,12 +2689,17 @@
       <c r="C96" s="9" t="n"/>
       <c r="D96" s="8" t="n"/>
       <c r="E96" s="8" t="n"/>
-      <c r="F96" s="10" t="n"/>
-      <c r="G96" s="11" t="n"/>
-      <c r="H96" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I96" s="8" t="inlineStr">
+      <c r="F96" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G96" s="10" t="n"/>
+      <c r="H96" s="11" t="n"/>
+      <c r="I96" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J96" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2247,12 +2711,17 @@
       <c r="C97" s="9" t="n"/>
       <c r="D97" s="8" t="n"/>
       <c r="E97" s="8" t="n"/>
-      <c r="F97" s="10" t="n"/>
-      <c r="G97" s="11" t="n"/>
-      <c r="H97" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I97" s="8" t="inlineStr">
+      <c r="F97" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G97" s="10" t="n"/>
+      <c r="H97" s="11" t="n"/>
+      <c r="I97" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J97" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2264,12 +2733,17 @@
       <c r="C98" s="9" t="n"/>
       <c r="D98" s="8" t="n"/>
       <c r="E98" s="8" t="n"/>
-      <c r="F98" s="10" t="n"/>
-      <c r="G98" s="11" t="n"/>
-      <c r="H98" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I98" s="8" t="inlineStr">
+      <c r="F98" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G98" s="10" t="n"/>
+      <c r="H98" s="11" t="n"/>
+      <c r="I98" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J98" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2281,12 +2755,17 @@
       <c r="C99" s="9" t="n"/>
       <c r="D99" s="8" t="n"/>
       <c r="E99" s="8" t="n"/>
-      <c r="F99" s="10" t="n"/>
-      <c r="G99" s="11" t="n"/>
-      <c r="H99" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I99" s="8" t="inlineStr">
+      <c r="F99" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G99" s="10" t="n"/>
+      <c r="H99" s="11" t="n"/>
+      <c r="I99" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J99" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2298,12 +2777,17 @@
       <c r="C100" s="9" t="n"/>
       <c r="D100" s="8" t="n"/>
       <c r="E100" s="8" t="n"/>
-      <c r="F100" s="10" t="n"/>
-      <c r="G100" s="11" t="n"/>
-      <c r="H100" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I100" s="8" t="inlineStr">
+      <c r="F100" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G100" s="10" t="n"/>
+      <c r="H100" s="11" t="n"/>
+      <c r="I100" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J100" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2315,12 +2799,17 @@
       <c r="C101" s="9" t="n"/>
       <c r="D101" s="8" t="n"/>
       <c r="E101" s="8" t="n"/>
-      <c r="F101" s="10" t="n"/>
-      <c r="G101" s="11" t="n"/>
-      <c r="H101" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I101" s="8" t="inlineStr">
+      <c r="F101" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G101" s="10" t="n"/>
+      <c r="H101" s="11" t="n"/>
+      <c r="I101" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J101" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2332,12 +2821,17 @@
       <c r="C102" s="9" t="n"/>
       <c r="D102" s="8" t="n"/>
       <c r="E102" s="8" t="n"/>
-      <c r="F102" s="10" t="n"/>
-      <c r="G102" s="11" t="n"/>
-      <c r="H102" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I102" s="8" t="inlineStr">
+      <c r="F102" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G102" s="10" t="n"/>
+      <c r="H102" s="11" t="n"/>
+      <c r="I102" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J102" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2349,12 +2843,17 @@
       <c r="C103" s="9" t="n"/>
       <c r="D103" s="8" t="n"/>
       <c r="E103" s="8" t="n"/>
-      <c r="F103" s="10" t="n"/>
-      <c r="G103" s="11" t="n"/>
-      <c r="H103" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I103" s="8" t="inlineStr">
+      <c r="F103" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G103" s="10" t="n"/>
+      <c r="H103" s="11" t="n"/>
+      <c r="I103" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J103" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2366,12 +2865,17 @@
       <c r="C104" s="9" t="n"/>
       <c r="D104" s="8" t="n"/>
       <c r="E104" s="8" t="n"/>
-      <c r="F104" s="10" t="n"/>
-      <c r="G104" s="11" t="n"/>
-      <c r="H104" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I104" s="8" t="inlineStr">
+      <c r="F104" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G104" s="10" t="n"/>
+      <c r="H104" s="11" t="n"/>
+      <c r="I104" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J104" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2383,12 +2887,17 @@
       <c r="C105" s="9" t="n"/>
       <c r="D105" s="8" t="n"/>
       <c r="E105" s="8" t="n"/>
-      <c r="F105" s="10" t="n"/>
-      <c r="G105" s="11" t="n"/>
-      <c r="H105" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I105" s="8" t="inlineStr">
+      <c r="F105" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G105" s="10" t="n"/>
+      <c r="H105" s="11" t="n"/>
+      <c r="I105" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J105" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2400,12 +2909,17 @@
       <c r="C106" s="9" t="n"/>
       <c r="D106" s="8" t="n"/>
       <c r="E106" s="8" t="n"/>
-      <c r="F106" s="10" t="n"/>
-      <c r="G106" s="11" t="n"/>
-      <c r="H106" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I106" s="8" t="inlineStr">
+      <c r="F106" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G106" s="10" t="n"/>
+      <c r="H106" s="11" t="n"/>
+      <c r="I106" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J106" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2417,12 +2931,17 @@
       <c r="C107" s="9" t="n"/>
       <c r="D107" s="8" t="n"/>
       <c r="E107" s="8" t="n"/>
-      <c r="F107" s="10" t="n"/>
-      <c r="G107" s="11" t="n"/>
-      <c r="H107" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I107" s="8" t="inlineStr">
+      <c r="F107" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G107" s="10" t="n"/>
+      <c r="H107" s="11" t="n"/>
+      <c r="I107" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J107" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2434,12 +2953,17 @@
       <c r="C108" s="9" t="n"/>
       <c r="D108" s="8" t="n"/>
       <c r="E108" s="8" t="n"/>
-      <c r="F108" s="10" t="n"/>
-      <c r="G108" s="11" t="n"/>
-      <c r="H108" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I108" s="8" t="inlineStr">
+      <c r="F108" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G108" s="10" t="n"/>
+      <c r="H108" s="11" t="n"/>
+      <c r="I108" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J108" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2451,12 +2975,17 @@
       <c r="C109" s="9" t="n"/>
       <c r="D109" s="8" t="n"/>
       <c r="E109" s="8" t="n"/>
-      <c r="F109" s="10" t="n"/>
-      <c r="G109" s="11" t="n"/>
-      <c r="H109" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I109" s="8" t="inlineStr">
+      <c r="F109" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G109" s="10" t="n"/>
+      <c r="H109" s="11" t="n"/>
+      <c r="I109" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J109" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2468,12 +2997,17 @@
       <c r="C110" s="9" t="n"/>
       <c r="D110" s="8" t="n"/>
       <c r="E110" s="8" t="n"/>
-      <c r="F110" s="10" t="n"/>
-      <c r="G110" s="11" t="n"/>
-      <c r="H110" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I110" s="8" t="inlineStr">
+      <c r="F110" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G110" s="10" t="n"/>
+      <c r="H110" s="11" t="n"/>
+      <c r="I110" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J110" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2485,12 +3019,17 @@
       <c r="C111" s="9" t="n"/>
       <c r="D111" s="8" t="n"/>
       <c r="E111" s="8" t="n"/>
-      <c r="F111" s="10" t="n"/>
-      <c r="G111" s="11" t="n"/>
-      <c r="H111" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I111" s="8" t="inlineStr">
+      <c r="F111" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G111" s="10" t="n"/>
+      <c r="H111" s="11" t="n"/>
+      <c r="I111" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J111" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2502,12 +3041,17 @@
       <c r="C112" s="9" t="n"/>
       <c r="D112" s="8" t="n"/>
       <c r="E112" s="8" t="n"/>
-      <c r="F112" s="10" t="n"/>
-      <c r="G112" s="11" t="n"/>
-      <c r="H112" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I112" s="8" t="inlineStr">
+      <c r="F112" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G112" s="10" t="n"/>
+      <c r="H112" s="11" t="n"/>
+      <c r="I112" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J112" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2519,12 +3063,17 @@
       <c r="C113" s="9" t="n"/>
       <c r="D113" s="8" t="n"/>
       <c r="E113" s="8" t="n"/>
-      <c r="F113" s="10" t="n"/>
-      <c r="G113" s="11" t="n"/>
-      <c r="H113" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I113" s="8" t="inlineStr">
+      <c r="F113" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G113" s="10" t="n"/>
+      <c r="H113" s="11" t="n"/>
+      <c r="I113" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J113" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2536,12 +3085,17 @@
       <c r="C114" s="9" t="n"/>
       <c r="D114" s="8" t="n"/>
       <c r="E114" s="8" t="n"/>
-      <c r="F114" s="10" t="n"/>
-      <c r="G114" s="11" t="n"/>
-      <c r="H114" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I114" s="8" t="inlineStr">
+      <c r="F114" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G114" s="10" t="n"/>
+      <c r="H114" s="11" t="n"/>
+      <c r="I114" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J114" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2553,12 +3107,17 @@
       <c r="C115" s="9" t="n"/>
       <c r="D115" s="8" t="n"/>
       <c r="E115" s="8" t="n"/>
-      <c r="F115" s="10" t="n"/>
-      <c r="G115" s="11" t="n"/>
-      <c r="H115" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I115" s="8" t="inlineStr">
+      <c r="F115" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G115" s="10" t="n"/>
+      <c r="H115" s="11" t="n"/>
+      <c r="I115" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J115" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2570,12 +3129,17 @@
       <c r="C116" s="9" t="n"/>
       <c r="D116" s="8" t="n"/>
       <c r="E116" s="8" t="n"/>
-      <c r="F116" s="10" t="n"/>
-      <c r="G116" s="11" t="n"/>
-      <c r="H116" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I116" s="8" t="inlineStr">
+      <c r="F116" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G116" s="10" t="n"/>
+      <c r="H116" s="11" t="n"/>
+      <c r="I116" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J116" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2587,12 +3151,17 @@
       <c r="C117" s="9" t="n"/>
       <c r="D117" s="8" t="n"/>
       <c r="E117" s="8" t="n"/>
-      <c r="F117" s="10" t="n"/>
-      <c r="G117" s="11" t="n"/>
-      <c r="H117" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I117" s="8" t="inlineStr">
+      <c r="F117" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G117" s="10" t="n"/>
+      <c r="H117" s="11" t="n"/>
+      <c r="I117" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J117" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2604,12 +3173,17 @@
       <c r="C118" s="9" t="n"/>
       <c r="D118" s="8" t="n"/>
       <c r="E118" s="8" t="n"/>
-      <c r="F118" s="10" t="n"/>
-      <c r="G118" s="11" t="n"/>
-      <c r="H118" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I118" s="8" t="inlineStr">
+      <c r="F118" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G118" s="10" t="n"/>
+      <c r="H118" s="11" t="n"/>
+      <c r="I118" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J118" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2621,12 +3195,17 @@
       <c r="C119" s="9" t="n"/>
       <c r="D119" s="8" t="n"/>
       <c r="E119" s="8" t="n"/>
-      <c r="F119" s="10" t="n"/>
-      <c r="G119" s="11" t="n"/>
-      <c r="H119" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I119" s="8" t="inlineStr">
+      <c r="F119" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G119" s="10" t="n"/>
+      <c r="H119" s="11" t="n"/>
+      <c r="I119" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J119" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2638,12 +3217,17 @@
       <c r="C120" s="9" t="n"/>
       <c r="D120" s="8" t="n"/>
       <c r="E120" s="8" t="n"/>
-      <c r="F120" s="10" t="n"/>
-      <c r="G120" s="11" t="n"/>
-      <c r="H120" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I120" s="8" t="inlineStr">
+      <c r="F120" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G120" s="10" t="n"/>
+      <c r="H120" s="11" t="n"/>
+      <c r="I120" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J120" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2655,12 +3239,17 @@
       <c r="C121" s="9" t="n"/>
       <c r="D121" s="8" t="n"/>
       <c r="E121" s="8" t="n"/>
-      <c r="F121" s="10" t="n"/>
-      <c r="G121" s="11" t="n"/>
-      <c r="H121" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I121" s="8" t="inlineStr">
+      <c r="F121" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G121" s="10" t="n"/>
+      <c r="H121" s="11" t="n"/>
+      <c r="I121" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J121" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2672,12 +3261,17 @@
       <c r="C122" s="9" t="n"/>
       <c r="D122" s="8" t="n"/>
       <c r="E122" s="8" t="n"/>
-      <c r="F122" s="10" t="n"/>
-      <c r="G122" s="11" t="n"/>
-      <c r="H122" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I122" s="8" t="inlineStr">
+      <c r="F122" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G122" s="10" t="n"/>
+      <c r="H122" s="11" t="n"/>
+      <c r="I122" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J122" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2689,12 +3283,17 @@
       <c r="C123" s="9" t="n"/>
       <c r="D123" s="8" t="n"/>
       <c r="E123" s="8" t="n"/>
-      <c r="F123" s="10" t="n"/>
-      <c r="G123" s="11" t="n"/>
-      <c r="H123" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I123" s="8" t="inlineStr">
+      <c r="F123" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G123" s="10" t="n"/>
+      <c r="H123" s="11" t="n"/>
+      <c r="I123" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J123" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2706,12 +3305,17 @@
       <c r="C124" s="9" t="n"/>
       <c r="D124" s="8" t="n"/>
       <c r="E124" s="8" t="n"/>
-      <c r="F124" s="10" t="n"/>
-      <c r="G124" s="11" t="n"/>
-      <c r="H124" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I124" s="8" t="inlineStr">
+      <c r="F124" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G124" s="10" t="n"/>
+      <c r="H124" s="11" t="n"/>
+      <c r="I124" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J124" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2723,12 +3327,17 @@
       <c r="C125" s="9" t="n"/>
       <c r="D125" s="8" t="n"/>
       <c r="E125" s="8" t="n"/>
-      <c r="F125" s="10" t="n"/>
-      <c r="G125" s="11" t="n"/>
-      <c r="H125" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I125" s="8" t="inlineStr">
+      <c r="F125" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G125" s="10" t="n"/>
+      <c r="H125" s="11" t="n"/>
+      <c r="I125" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J125" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2740,12 +3349,17 @@
       <c r="C126" s="9" t="n"/>
       <c r="D126" s="8" t="n"/>
       <c r="E126" s="8" t="n"/>
-      <c r="F126" s="10" t="n"/>
-      <c r="G126" s="11" t="n"/>
-      <c r="H126" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I126" s="8" t="inlineStr">
+      <c r="F126" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G126" s="10" t="n"/>
+      <c r="H126" s="11" t="n"/>
+      <c r="I126" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J126" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2757,12 +3371,17 @@
       <c r="C127" s="9" t="n"/>
       <c r="D127" s="8" t="n"/>
       <c r="E127" s="8" t="n"/>
-      <c r="F127" s="10" t="n"/>
-      <c r="G127" s="11" t="n"/>
-      <c r="H127" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I127" s="8" t="inlineStr">
+      <c r="F127" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G127" s="10" t="n"/>
+      <c r="H127" s="11" t="n"/>
+      <c r="I127" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J127" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2774,12 +3393,17 @@
       <c r="C128" s="9" t="n"/>
       <c r="D128" s="8" t="n"/>
       <c r="E128" s="8" t="n"/>
-      <c r="F128" s="10" t="n"/>
-      <c r="G128" s="11" t="n"/>
-      <c r="H128" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I128" s="8" t="inlineStr">
+      <c r="F128" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G128" s="10" t="n"/>
+      <c r="H128" s="11" t="n"/>
+      <c r="I128" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J128" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2791,12 +3415,17 @@
       <c r="C129" s="9" t="n"/>
       <c r="D129" s="8" t="n"/>
       <c r="E129" s="8" t="n"/>
-      <c r="F129" s="10" t="n"/>
-      <c r="G129" s="11" t="n"/>
-      <c r="H129" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I129" s="8" t="inlineStr">
+      <c r="F129" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G129" s="10" t="n"/>
+      <c r="H129" s="11" t="n"/>
+      <c r="I129" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J129" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2808,12 +3437,17 @@
       <c r="C130" s="9" t="n"/>
       <c r="D130" s="8" t="n"/>
       <c r="E130" s="8" t="n"/>
-      <c r="F130" s="10" t="n"/>
-      <c r="G130" s="11" t="n"/>
-      <c r="H130" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I130" s="8" t="inlineStr">
+      <c r="F130" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G130" s="10" t="n"/>
+      <c r="H130" s="11" t="n"/>
+      <c r="I130" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J130" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2825,12 +3459,17 @@
       <c r="C131" s="9" t="n"/>
       <c r="D131" s="8" t="n"/>
       <c r="E131" s="8" t="n"/>
-      <c r="F131" s="10" t="n"/>
-      <c r="G131" s="11" t="n"/>
-      <c r="H131" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I131" s="8" t="inlineStr">
+      <c r="F131" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G131" s="10" t="n"/>
+      <c r="H131" s="11" t="n"/>
+      <c r="I131" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J131" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2842,12 +3481,17 @@
       <c r="C132" s="9" t="n"/>
       <c r="D132" s="8" t="n"/>
       <c r="E132" s="8" t="n"/>
-      <c r="F132" s="10" t="n"/>
-      <c r="G132" s="11" t="n"/>
-      <c r="H132" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I132" s="8" t="inlineStr">
+      <c r="F132" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G132" s="10" t="n"/>
+      <c r="H132" s="11" t="n"/>
+      <c r="I132" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J132" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2859,12 +3503,17 @@
       <c r="C133" s="9" t="n"/>
       <c r="D133" s="8" t="n"/>
       <c r="E133" s="8" t="n"/>
-      <c r="F133" s="10" t="n"/>
-      <c r="G133" s="11" t="n"/>
-      <c r="H133" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I133" s="8" t="inlineStr">
+      <c r="F133" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G133" s="10" t="n"/>
+      <c r="H133" s="11" t="n"/>
+      <c r="I133" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J133" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2876,12 +3525,17 @@
       <c r="C134" s="9" t="n"/>
       <c r="D134" s="8" t="n"/>
       <c r="E134" s="8" t="n"/>
-      <c r="F134" s="10" t="n"/>
-      <c r="G134" s="11" t="n"/>
-      <c r="H134" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I134" s="8" t="inlineStr">
+      <c r="F134" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G134" s="10" t="n"/>
+      <c r="H134" s="11" t="n"/>
+      <c r="I134" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J134" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2893,12 +3547,17 @@
       <c r="C135" s="9" t="n"/>
       <c r="D135" s="8" t="n"/>
       <c r="E135" s="8" t="n"/>
-      <c r="F135" s="10" t="n"/>
-      <c r="G135" s="11" t="n"/>
-      <c r="H135" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I135" s="8" t="inlineStr">
+      <c r="F135" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G135" s="10" t="n"/>
+      <c r="H135" s="11" t="n"/>
+      <c r="I135" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J135" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2910,12 +3569,17 @@
       <c r="C136" s="9" t="n"/>
       <c r="D136" s="8" t="n"/>
       <c r="E136" s="8" t="n"/>
-      <c r="F136" s="10" t="n"/>
-      <c r="G136" s="11" t="n"/>
-      <c r="H136" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I136" s="8" t="inlineStr">
+      <c r="F136" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G136" s="10" t="n"/>
+      <c r="H136" s="11" t="n"/>
+      <c r="I136" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J136" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2927,12 +3591,17 @@
       <c r="C137" s="9" t="n"/>
       <c r="D137" s="8" t="n"/>
       <c r="E137" s="8" t="n"/>
-      <c r="F137" s="10" t="n"/>
-      <c r="G137" s="11" t="n"/>
-      <c r="H137" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I137" s="8" t="inlineStr">
+      <c r="F137" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G137" s="10" t="n"/>
+      <c r="H137" s="11" t="n"/>
+      <c r="I137" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J137" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2944,12 +3613,17 @@
       <c r="C138" s="9" t="n"/>
       <c r="D138" s="8" t="n"/>
       <c r="E138" s="8" t="n"/>
-      <c r="F138" s="10" t="n"/>
-      <c r="G138" s="11" t="n"/>
-      <c r="H138" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I138" s="8" t="inlineStr">
+      <c r="F138" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G138" s="10" t="n"/>
+      <c r="H138" s="11" t="n"/>
+      <c r="I138" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J138" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2961,12 +3635,17 @@
       <c r="C139" s="9" t="n"/>
       <c r="D139" s="8" t="n"/>
       <c r="E139" s="8" t="n"/>
-      <c r="F139" s="10" t="n"/>
-      <c r="G139" s="11" t="n"/>
-      <c r="H139" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I139" s="8" t="inlineStr">
+      <c r="F139" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G139" s="10" t="n"/>
+      <c r="H139" s="11" t="n"/>
+      <c r="I139" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J139" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2978,12 +3657,17 @@
       <c r="C140" s="9" t="n"/>
       <c r="D140" s="8" t="n"/>
       <c r="E140" s="8" t="n"/>
-      <c r="F140" s="10" t="n"/>
-      <c r="G140" s="11" t="n"/>
-      <c r="H140" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I140" s="8" t="inlineStr">
+      <c r="F140" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G140" s="10" t="n"/>
+      <c r="H140" s="11" t="n"/>
+      <c r="I140" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J140" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -2995,12 +3679,17 @@
       <c r="C141" s="9" t="n"/>
       <c r="D141" s="8" t="n"/>
       <c r="E141" s="8" t="n"/>
-      <c r="F141" s="10" t="n"/>
-      <c r="G141" s="11" t="n"/>
-      <c r="H141" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I141" s="8" t="inlineStr">
+      <c r="F141" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G141" s="10" t="n"/>
+      <c r="H141" s="11" t="n"/>
+      <c r="I141" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J141" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3012,12 +3701,17 @@
       <c r="C142" s="9" t="n"/>
       <c r="D142" s="8" t="n"/>
       <c r="E142" s="8" t="n"/>
-      <c r="F142" s="10" t="n"/>
-      <c r="G142" s="11" t="n"/>
-      <c r="H142" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I142" s="8" t="inlineStr">
+      <c r="F142" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G142" s="10" t="n"/>
+      <c r="H142" s="11" t="n"/>
+      <c r="I142" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J142" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3029,12 +3723,17 @@
       <c r="C143" s="9" t="n"/>
       <c r="D143" s="8" t="n"/>
       <c r="E143" s="8" t="n"/>
-      <c r="F143" s="10" t="n"/>
-      <c r="G143" s="11" t="n"/>
-      <c r="H143" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I143" s="8" t="inlineStr">
+      <c r="F143" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G143" s="10" t="n"/>
+      <c r="H143" s="11" t="n"/>
+      <c r="I143" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J143" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3046,12 +3745,17 @@
       <c r="C144" s="9" t="n"/>
       <c r="D144" s="8" t="n"/>
       <c r="E144" s="8" t="n"/>
-      <c r="F144" s="10" t="n"/>
-      <c r="G144" s="11" t="n"/>
-      <c r="H144" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I144" s="8" t="inlineStr">
+      <c r="F144" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G144" s="10" t="n"/>
+      <c r="H144" s="11" t="n"/>
+      <c r="I144" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J144" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3063,12 +3767,17 @@
       <c r="C145" s="9" t="n"/>
       <c r="D145" s="8" t="n"/>
       <c r="E145" s="8" t="n"/>
-      <c r="F145" s="10" t="n"/>
-      <c r="G145" s="11" t="n"/>
-      <c r="H145" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I145" s="8" t="inlineStr">
+      <c r="F145" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G145" s="10" t="n"/>
+      <c r="H145" s="11" t="n"/>
+      <c r="I145" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J145" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3080,12 +3789,17 @@
       <c r="C146" s="9" t="n"/>
       <c r="D146" s="8" t="n"/>
       <c r="E146" s="8" t="n"/>
-      <c r="F146" s="10" t="n"/>
-      <c r="G146" s="11" t="n"/>
-      <c r="H146" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I146" s="8" t="inlineStr">
+      <c r="F146" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G146" s="10" t="n"/>
+      <c r="H146" s="11" t="n"/>
+      <c r="I146" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J146" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3097,12 +3811,17 @@
       <c r="C147" s="9" t="n"/>
       <c r="D147" s="8" t="n"/>
       <c r="E147" s="8" t="n"/>
-      <c r="F147" s="10" t="n"/>
-      <c r="G147" s="11" t="n"/>
-      <c r="H147" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I147" s="8" t="inlineStr">
+      <c r="F147" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G147" s="10" t="n"/>
+      <c r="H147" s="11" t="n"/>
+      <c r="I147" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J147" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3114,12 +3833,17 @@
       <c r="C148" s="9" t="n"/>
       <c r="D148" s="8" t="n"/>
       <c r="E148" s="8" t="n"/>
-      <c r="F148" s="10" t="n"/>
-      <c r="G148" s="11" t="n"/>
-      <c r="H148" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I148" s="8" t="inlineStr">
+      <c r="F148" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G148" s="10" t="n"/>
+      <c r="H148" s="11" t="n"/>
+      <c r="I148" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J148" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3131,12 +3855,17 @@
       <c r="C149" s="9" t="n"/>
       <c r="D149" s="8" t="n"/>
       <c r="E149" s="8" t="n"/>
-      <c r="F149" s="10" t="n"/>
-      <c r="G149" s="11" t="n"/>
-      <c r="H149" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I149" s="8" t="inlineStr">
+      <c r="F149" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G149" s="10" t="n"/>
+      <c r="H149" s="11" t="n"/>
+      <c r="I149" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J149" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3148,12 +3877,17 @@
       <c r="C150" s="9" t="n"/>
       <c r="D150" s="8" t="n"/>
       <c r="E150" s="8" t="n"/>
-      <c r="F150" s="10" t="n"/>
-      <c r="G150" s="11" t="n"/>
-      <c r="H150" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I150" s="8" t="inlineStr">
+      <c r="F150" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G150" s="10" t="n"/>
+      <c r="H150" s="11" t="n"/>
+      <c r="I150" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J150" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3165,12 +3899,17 @@
       <c r="C151" s="9" t="n"/>
       <c r="D151" s="8" t="n"/>
       <c r="E151" s="8" t="n"/>
-      <c r="F151" s="10" t="n"/>
-      <c r="G151" s="11" t="n"/>
-      <c r="H151" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I151" s="8" t="inlineStr">
+      <c r="F151" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G151" s="10" t="n"/>
+      <c r="H151" s="11" t="n"/>
+      <c r="I151" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J151" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3182,12 +3921,17 @@
       <c r="C152" s="9" t="n"/>
       <c r="D152" s="8" t="n"/>
       <c r="E152" s="8" t="n"/>
-      <c r="F152" s="10" t="n"/>
-      <c r="G152" s="11" t="n"/>
-      <c r="H152" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I152" s="8" t="inlineStr">
+      <c r="F152" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G152" s="10" t="n"/>
+      <c r="H152" s="11" t="n"/>
+      <c r="I152" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J152" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3199,12 +3943,17 @@
       <c r="C153" s="9" t="n"/>
       <c r="D153" s="8" t="n"/>
       <c r="E153" s="8" t="n"/>
-      <c r="F153" s="10" t="n"/>
-      <c r="G153" s="11" t="n"/>
-      <c r="H153" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I153" s="8" t="inlineStr">
+      <c r="F153" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G153" s="10" t="n"/>
+      <c r="H153" s="11" t="n"/>
+      <c r="I153" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J153" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3216,12 +3965,17 @@
       <c r="C154" s="9" t="n"/>
       <c r="D154" s="8" t="n"/>
       <c r="E154" s="8" t="n"/>
-      <c r="F154" s="10" t="n"/>
-      <c r="G154" s="11" t="n"/>
-      <c r="H154" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I154" s="8" t="inlineStr">
+      <c r="F154" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G154" s="10" t="n"/>
+      <c r="H154" s="11" t="n"/>
+      <c r="I154" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J154" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3233,12 +3987,17 @@
       <c r="C155" s="9" t="n"/>
       <c r="D155" s="8" t="n"/>
       <c r="E155" s="8" t="n"/>
-      <c r="F155" s="10" t="n"/>
-      <c r="G155" s="11" t="n"/>
-      <c r="H155" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I155" s="8" t="inlineStr">
+      <c r="F155" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G155" s="10" t="n"/>
+      <c r="H155" s="11" t="n"/>
+      <c r="I155" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J155" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3250,12 +4009,17 @@
       <c r="C156" s="9" t="n"/>
       <c r="D156" s="8" t="n"/>
       <c r="E156" s="8" t="n"/>
-      <c r="F156" s="10" t="n"/>
-      <c r="G156" s="11" t="n"/>
-      <c r="H156" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I156" s="8" t="inlineStr">
+      <c r="F156" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G156" s="10" t="n"/>
+      <c r="H156" s="11" t="n"/>
+      <c r="I156" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J156" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3267,12 +4031,17 @@
       <c r="C157" s="9" t="n"/>
       <c r="D157" s="8" t="n"/>
       <c r="E157" s="8" t="n"/>
-      <c r="F157" s="10" t="n"/>
-      <c r="G157" s="11" t="n"/>
-      <c r="H157" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I157" s="8" t="inlineStr">
+      <c r="F157" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G157" s="10" t="n"/>
+      <c r="H157" s="11" t="n"/>
+      <c r="I157" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J157" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3284,12 +4053,17 @@
       <c r="C158" s="9" t="n"/>
       <c r="D158" s="8" t="n"/>
       <c r="E158" s="8" t="n"/>
-      <c r="F158" s="10" t="n"/>
-      <c r="G158" s="11" t="n"/>
-      <c r="H158" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I158" s="8" t="inlineStr">
+      <c r="F158" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G158" s="10" t="n"/>
+      <c r="H158" s="11" t="n"/>
+      <c r="I158" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J158" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3301,12 +4075,17 @@
       <c r="C159" s="9" t="n"/>
       <c r="D159" s="8" t="n"/>
       <c r="E159" s="8" t="n"/>
-      <c r="F159" s="10" t="n"/>
-      <c r="G159" s="11" t="n"/>
-      <c r="H159" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I159" s="8" t="inlineStr">
+      <c r="F159" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G159" s="10" t="n"/>
+      <c r="H159" s="11" t="n"/>
+      <c r="I159" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J159" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3318,12 +4097,17 @@
       <c r="C160" s="9" t="n"/>
       <c r="D160" s="8" t="n"/>
       <c r="E160" s="8" t="n"/>
-      <c r="F160" s="10" t="n"/>
-      <c r="G160" s="11" t="n"/>
-      <c r="H160" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I160" s="8" t="inlineStr">
+      <c r="F160" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G160" s="10" t="n"/>
+      <c r="H160" s="11" t="n"/>
+      <c r="I160" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J160" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3335,12 +4119,17 @@
       <c r="C161" s="9" t="n"/>
       <c r="D161" s="8" t="n"/>
       <c r="E161" s="8" t="n"/>
-      <c r="F161" s="10" t="n"/>
-      <c r="G161" s="11" t="n"/>
-      <c r="H161" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I161" s="8" t="inlineStr">
+      <c r="F161" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G161" s="10" t="n"/>
+      <c r="H161" s="11" t="n"/>
+      <c r="I161" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J161" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3352,12 +4141,17 @@
       <c r="C162" s="9" t="n"/>
       <c r="D162" s="8" t="n"/>
       <c r="E162" s="8" t="n"/>
-      <c r="F162" s="10" t="n"/>
-      <c r="G162" s="11" t="n"/>
-      <c r="H162" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I162" s="8" t="inlineStr">
+      <c r="F162" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G162" s="10" t="n"/>
+      <c r="H162" s="11" t="n"/>
+      <c r="I162" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J162" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3369,12 +4163,17 @@
       <c r="C163" s="9" t="n"/>
       <c r="D163" s="8" t="n"/>
       <c r="E163" s="8" t="n"/>
-      <c r="F163" s="10" t="n"/>
-      <c r="G163" s="11" t="n"/>
-      <c r="H163" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I163" s="8" t="inlineStr">
+      <c r="F163" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G163" s="10" t="n"/>
+      <c r="H163" s="11" t="n"/>
+      <c r="I163" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J163" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3386,12 +4185,17 @@
       <c r="C164" s="9" t="n"/>
       <c r="D164" s="8" t="n"/>
       <c r="E164" s="8" t="n"/>
-      <c r="F164" s="10" t="n"/>
-      <c r="G164" s="11" t="n"/>
-      <c r="H164" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I164" s="8" t="inlineStr">
+      <c r="F164" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G164" s="10" t="n"/>
+      <c r="H164" s="11" t="n"/>
+      <c r="I164" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J164" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3403,12 +4207,17 @@
       <c r="C165" s="9" t="n"/>
       <c r="D165" s="8" t="n"/>
       <c r="E165" s="8" t="n"/>
-      <c r="F165" s="10" t="n"/>
-      <c r="G165" s="11" t="n"/>
-      <c r="H165" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I165" s="8" t="inlineStr">
+      <c r="F165" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G165" s="10" t="n"/>
+      <c r="H165" s="11" t="n"/>
+      <c r="I165" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J165" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3420,12 +4229,17 @@
       <c r="C166" s="9" t="n"/>
       <c r="D166" s="8" t="n"/>
       <c r="E166" s="8" t="n"/>
-      <c r="F166" s="10" t="n"/>
-      <c r="G166" s="11" t="n"/>
-      <c r="H166" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I166" s="8" t="inlineStr">
+      <c r="F166" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G166" s="10" t="n"/>
+      <c r="H166" s="11" t="n"/>
+      <c r="I166" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J166" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3437,12 +4251,17 @@
       <c r="C167" s="9" t="n"/>
       <c r="D167" s="8" t="n"/>
       <c r="E167" s="8" t="n"/>
-      <c r="F167" s="10" t="n"/>
-      <c r="G167" s="11" t="n"/>
-      <c r="H167" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I167" s="8" t="inlineStr">
+      <c r="F167" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G167" s="10" t="n"/>
+      <c r="H167" s="11" t="n"/>
+      <c r="I167" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J167" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3454,12 +4273,17 @@
       <c r="C168" s="9" t="n"/>
       <c r="D168" s="8" t="n"/>
       <c r="E168" s="8" t="n"/>
-      <c r="F168" s="10" t="n"/>
-      <c r="G168" s="11" t="n"/>
-      <c r="H168" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I168" s="8" t="inlineStr">
+      <c r="F168" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G168" s="10" t="n"/>
+      <c r="H168" s="11" t="n"/>
+      <c r="I168" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J168" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3471,12 +4295,17 @@
       <c r="C169" s="9" t="n"/>
       <c r="D169" s="8" t="n"/>
       <c r="E169" s="8" t="n"/>
-      <c r="F169" s="10" t="n"/>
-      <c r="G169" s="11" t="n"/>
-      <c r="H169" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I169" s="8" t="inlineStr">
+      <c r="F169" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G169" s="10" t="n"/>
+      <c r="H169" s="11" t="n"/>
+      <c r="I169" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J169" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3488,12 +4317,17 @@
       <c r="C170" s="9" t="n"/>
       <c r="D170" s="8" t="n"/>
       <c r="E170" s="8" t="n"/>
-      <c r="F170" s="10" t="n"/>
-      <c r="G170" s="11" t="n"/>
-      <c r="H170" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I170" s="8" t="inlineStr">
+      <c r="F170" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G170" s="10" t="n"/>
+      <c r="H170" s="11" t="n"/>
+      <c r="I170" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J170" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3505,12 +4339,17 @@
       <c r="C171" s="9" t="n"/>
       <c r="D171" s="8" t="n"/>
       <c r="E171" s="8" t="n"/>
-      <c r="F171" s="10" t="n"/>
-      <c r="G171" s="11" t="n"/>
-      <c r="H171" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I171" s="8" t="inlineStr">
+      <c r="F171" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G171" s="10" t="n"/>
+      <c r="H171" s="11" t="n"/>
+      <c r="I171" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J171" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3522,12 +4361,17 @@
       <c r="C172" s="9" t="n"/>
       <c r="D172" s="8" t="n"/>
       <c r="E172" s="8" t="n"/>
-      <c r="F172" s="10" t="n"/>
-      <c r="G172" s="11" t="n"/>
-      <c r="H172" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I172" s="8" t="inlineStr">
+      <c r="F172" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G172" s="10" t="n"/>
+      <c r="H172" s="11" t="n"/>
+      <c r="I172" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J172" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3539,12 +4383,17 @@
       <c r="C173" s="9" t="n"/>
       <c r="D173" s="8" t="n"/>
       <c r="E173" s="8" t="n"/>
-      <c r="F173" s="10" t="n"/>
-      <c r="G173" s="11" t="n"/>
-      <c r="H173" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I173" s="8" t="inlineStr">
+      <c r="F173" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G173" s="10" t="n"/>
+      <c r="H173" s="11" t="n"/>
+      <c r="I173" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J173" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3556,12 +4405,17 @@
       <c r="C174" s="9" t="n"/>
       <c r="D174" s="8" t="n"/>
       <c r="E174" s="8" t="n"/>
-      <c r="F174" s="10" t="n"/>
-      <c r="G174" s="11" t="n"/>
-      <c r="H174" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I174" s="8" t="inlineStr">
+      <c r="F174" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G174" s="10" t="n"/>
+      <c r="H174" s="11" t="n"/>
+      <c r="I174" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J174" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3573,12 +4427,17 @@
       <c r="C175" s="9" t="n"/>
       <c r="D175" s="8" t="n"/>
       <c r="E175" s="8" t="n"/>
-      <c r="F175" s="10" t="n"/>
-      <c r="G175" s="11" t="n"/>
-      <c r="H175" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I175" s="8" t="inlineStr">
+      <c r="F175" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G175" s="10" t="n"/>
+      <c r="H175" s="11" t="n"/>
+      <c r="I175" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J175" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3590,12 +4449,17 @@
       <c r="C176" s="9" t="n"/>
       <c r="D176" s="8" t="n"/>
       <c r="E176" s="8" t="n"/>
-      <c r="F176" s="10" t="n"/>
-      <c r="G176" s="11" t="n"/>
-      <c r="H176" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I176" s="8" t="inlineStr">
+      <c r="F176" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G176" s="10" t="n"/>
+      <c r="H176" s="11" t="n"/>
+      <c r="I176" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J176" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3607,12 +4471,17 @@
       <c r="C177" s="9" t="n"/>
       <c r="D177" s="8" t="n"/>
       <c r="E177" s="8" t="n"/>
-      <c r="F177" s="10" t="n"/>
-      <c r="G177" s="11" t="n"/>
-      <c r="H177" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I177" s="8" t="inlineStr">
+      <c r="F177" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G177" s="10" t="n"/>
+      <c r="H177" s="11" t="n"/>
+      <c r="I177" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J177" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3624,12 +4493,17 @@
       <c r="C178" s="9" t="n"/>
       <c r="D178" s="8" t="n"/>
       <c r="E178" s="8" t="n"/>
-      <c r="F178" s="10" t="n"/>
-      <c r="G178" s="11" t="n"/>
-      <c r="H178" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I178" s="8" t="inlineStr">
+      <c r="F178" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G178" s="10" t="n"/>
+      <c r="H178" s="11" t="n"/>
+      <c r="I178" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J178" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3641,12 +4515,17 @@
       <c r="C179" s="9" t="n"/>
       <c r="D179" s="8" t="n"/>
       <c r="E179" s="8" t="n"/>
-      <c r="F179" s="10" t="n"/>
-      <c r="G179" s="11" t="n"/>
-      <c r="H179" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I179" s="8" t="inlineStr">
+      <c r="F179" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G179" s="10" t="n"/>
+      <c r="H179" s="11" t="n"/>
+      <c r="I179" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J179" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3658,12 +4537,17 @@
       <c r="C180" s="9" t="n"/>
       <c r="D180" s="8" t="n"/>
       <c r="E180" s="8" t="n"/>
-      <c r="F180" s="10" t="n"/>
-      <c r="G180" s="11" t="n"/>
-      <c r="H180" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I180" s="8" t="inlineStr">
+      <c r="F180" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G180" s="10" t="n"/>
+      <c r="H180" s="11" t="n"/>
+      <c r="I180" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J180" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3675,12 +4559,17 @@
       <c r="C181" s="9" t="n"/>
       <c r="D181" s="8" t="n"/>
       <c r="E181" s="8" t="n"/>
-      <c r="F181" s="10" t="n"/>
-      <c r="G181" s="11" t="n"/>
-      <c r="H181" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I181" s="8" t="inlineStr">
+      <c r="F181" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G181" s="10" t="n"/>
+      <c r="H181" s="11" t="n"/>
+      <c r="I181" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J181" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3692,12 +4581,17 @@
       <c r="C182" s="9" t="n"/>
       <c r="D182" s="8" t="n"/>
       <c r="E182" s="8" t="n"/>
-      <c r="F182" s="10" t="n"/>
-      <c r="G182" s="11" t="n"/>
-      <c r="H182" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I182" s="8" t="inlineStr">
+      <c r="F182" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G182" s="10" t="n"/>
+      <c r="H182" s="11" t="n"/>
+      <c r="I182" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J182" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3709,12 +4603,17 @@
       <c r="C183" s="9" t="n"/>
       <c r="D183" s="8" t="n"/>
       <c r="E183" s="8" t="n"/>
-      <c r="F183" s="10" t="n"/>
-      <c r="G183" s="11" t="n"/>
-      <c r="H183" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I183" s="8" t="inlineStr">
+      <c r="F183" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G183" s="10" t="n"/>
+      <c r="H183" s="11" t="n"/>
+      <c r="I183" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J183" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3726,12 +4625,17 @@
       <c r="C184" s="9" t="n"/>
       <c r="D184" s="8" t="n"/>
       <c r="E184" s="8" t="n"/>
-      <c r="F184" s="10" t="n"/>
-      <c r="G184" s="11" t="n"/>
-      <c r="H184" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I184" s="8" t="inlineStr">
+      <c r="F184" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G184" s="10" t="n"/>
+      <c r="H184" s="11" t="n"/>
+      <c r="I184" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J184" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3743,12 +4647,17 @@
       <c r="C185" s="9" t="n"/>
       <c r="D185" s="8" t="n"/>
       <c r="E185" s="8" t="n"/>
-      <c r="F185" s="10" t="n"/>
-      <c r="G185" s="11" t="n"/>
-      <c r="H185" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I185" s="8" t="inlineStr">
+      <c r="F185" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G185" s="10" t="n"/>
+      <c r="H185" s="11" t="n"/>
+      <c r="I185" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J185" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3760,12 +4669,17 @@
       <c r="C186" s="9" t="n"/>
       <c r="D186" s="8" t="n"/>
       <c r="E186" s="8" t="n"/>
-      <c r="F186" s="10" t="n"/>
-      <c r="G186" s="11" t="n"/>
-      <c r="H186" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I186" s="8" t="inlineStr">
+      <c r="F186" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G186" s="10" t="n"/>
+      <c r="H186" s="11" t="n"/>
+      <c r="I186" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J186" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3777,12 +4691,17 @@
       <c r="C187" s="9" t="n"/>
       <c r="D187" s="8" t="n"/>
       <c r="E187" s="8" t="n"/>
-      <c r="F187" s="10" t="n"/>
-      <c r="G187" s="11" t="n"/>
-      <c r="H187" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I187" s="8" t="inlineStr">
+      <c r="F187" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G187" s="10" t="n"/>
+      <c r="H187" s="11" t="n"/>
+      <c r="I187" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J187" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3794,12 +4713,17 @@
       <c r="C188" s="9" t="n"/>
       <c r="D188" s="8" t="n"/>
       <c r="E188" s="8" t="n"/>
-      <c r="F188" s="10" t="n"/>
-      <c r="G188" s="11" t="n"/>
-      <c r="H188" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I188" s="8" t="inlineStr">
+      <c r="F188" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G188" s="10" t="n"/>
+      <c r="H188" s="11" t="n"/>
+      <c r="I188" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J188" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3811,12 +4735,17 @@
       <c r="C189" s="9" t="n"/>
       <c r="D189" s="8" t="n"/>
       <c r="E189" s="8" t="n"/>
-      <c r="F189" s="10" t="n"/>
-      <c r="G189" s="11" t="n"/>
-      <c r="H189" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I189" s="8" t="inlineStr">
+      <c r="F189" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G189" s="10" t="n"/>
+      <c r="H189" s="11" t="n"/>
+      <c r="I189" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J189" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3828,12 +4757,17 @@
       <c r="C190" s="9" t="n"/>
       <c r="D190" s="8" t="n"/>
       <c r="E190" s="8" t="n"/>
-      <c r="F190" s="10" t="n"/>
-      <c r="G190" s="11" t="n"/>
-      <c r="H190" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I190" s="8" t="inlineStr">
+      <c r="F190" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G190" s="10" t="n"/>
+      <c r="H190" s="11" t="n"/>
+      <c r="I190" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J190" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3845,12 +4779,17 @@
       <c r="C191" s="9" t="n"/>
       <c r="D191" s="8" t="n"/>
       <c r="E191" s="8" t="n"/>
-      <c r="F191" s="10" t="n"/>
-      <c r="G191" s="11" t="n"/>
-      <c r="H191" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I191" s="8" t="inlineStr">
+      <c r="F191" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G191" s="10" t="n"/>
+      <c r="H191" s="11" t="n"/>
+      <c r="I191" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J191" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3862,12 +4801,17 @@
       <c r="C192" s="9" t="n"/>
       <c r="D192" s="8" t="n"/>
       <c r="E192" s="8" t="n"/>
-      <c r="F192" s="10" t="n"/>
-      <c r="G192" s="11" t="n"/>
-      <c r="H192" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I192" s="8" t="inlineStr">
+      <c r="F192" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G192" s="10" t="n"/>
+      <c r="H192" s="11" t="n"/>
+      <c r="I192" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J192" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3879,12 +4823,17 @@
       <c r="C193" s="9" t="n"/>
       <c r="D193" s="8" t="n"/>
       <c r="E193" s="8" t="n"/>
-      <c r="F193" s="10" t="n"/>
-      <c r="G193" s="11" t="n"/>
-      <c r="H193" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I193" s="8" t="inlineStr">
+      <c r="F193" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G193" s="10" t="n"/>
+      <c r="H193" s="11" t="n"/>
+      <c r="I193" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J193" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3896,12 +4845,17 @@
       <c r="C194" s="9" t="n"/>
       <c r="D194" s="8" t="n"/>
       <c r="E194" s="8" t="n"/>
-      <c r="F194" s="10" t="n"/>
-      <c r="G194" s="11" t="n"/>
-      <c r="H194" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I194" s="8" t="inlineStr">
+      <c r="F194" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G194" s="10" t="n"/>
+      <c r="H194" s="11" t="n"/>
+      <c r="I194" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J194" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3913,12 +4867,17 @@
       <c r="C195" s="9" t="n"/>
       <c r="D195" s="8" t="n"/>
       <c r="E195" s="8" t="n"/>
-      <c r="F195" s="10" t="n"/>
-      <c r="G195" s="11" t="n"/>
-      <c r="H195" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I195" s="8" t="inlineStr">
+      <c r="F195" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G195" s="10" t="n"/>
+      <c r="H195" s="11" t="n"/>
+      <c r="I195" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J195" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3930,12 +4889,17 @@
       <c r="C196" s="9" t="n"/>
       <c r="D196" s="8" t="n"/>
       <c r="E196" s="8" t="n"/>
-      <c r="F196" s="10" t="n"/>
-      <c r="G196" s="11" t="n"/>
-      <c r="H196" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I196" s="8" t="inlineStr">
+      <c r="F196" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G196" s="10" t="n"/>
+      <c r="H196" s="11" t="n"/>
+      <c r="I196" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J196" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3947,12 +4911,17 @@
       <c r="C197" s="9" t="n"/>
       <c r="D197" s="8" t="n"/>
       <c r="E197" s="8" t="n"/>
-      <c r="F197" s="10" t="n"/>
-      <c r="G197" s="11" t="n"/>
-      <c r="H197" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I197" s="8" t="inlineStr">
+      <c r="F197" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G197" s="10" t="n"/>
+      <c r="H197" s="11" t="n"/>
+      <c r="I197" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J197" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3964,12 +4933,17 @@
       <c r="C198" s="9" t="n"/>
       <c r="D198" s="8" t="n"/>
       <c r="E198" s="8" t="n"/>
-      <c r="F198" s="10" t="n"/>
-      <c r="G198" s="11" t="n"/>
-      <c r="H198" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I198" s="8" t="inlineStr">
+      <c r="F198" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G198" s="10" t="n"/>
+      <c r="H198" s="11" t="n"/>
+      <c r="I198" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J198" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3981,12 +4955,17 @@
       <c r="C199" s="9" t="n"/>
       <c r="D199" s="8" t="n"/>
       <c r="E199" s="8" t="n"/>
-      <c r="F199" s="10" t="n"/>
-      <c r="G199" s="11" t="n"/>
-      <c r="H199" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I199" s="8" t="inlineStr">
+      <c r="F199" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G199" s="10" t="n"/>
+      <c r="H199" s="11" t="n"/>
+      <c r="I199" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J199" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3998,12 +4977,17 @@
       <c r="C200" s="9" t="n"/>
       <c r="D200" s="8" t="n"/>
       <c r="E200" s="8" t="n"/>
-      <c r="F200" s="10" t="n"/>
-      <c r="G200" s="11" t="n"/>
-      <c r="H200" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I200" s="8" t="inlineStr">
+      <c r="F200" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G200" s="10" t="n"/>
+      <c r="H200" s="11" t="n"/>
+      <c r="I200" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J200" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4015,12 +4999,17 @@
       <c r="C201" s="9" t="n"/>
       <c r="D201" s="8" t="n"/>
       <c r="E201" s="8" t="n"/>
-      <c r="F201" s="10" t="n"/>
-      <c r="G201" s="11" t="n"/>
-      <c r="H201" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I201" s="8" t="inlineStr">
+      <c r="F201" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G201" s="10" t="n"/>
+      <c r="H201" s="11" t="n"/>
+      <c r="I201" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J201" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4032,12 +5021,17 @@
       <c r="C202" s="9" t="n"/>
       <c r="D202" s="8" t="n"/>
       <c r="E202" s="8" t="n"/>
-      <c r="F202" s="10" t="n"/>
-      <c r="G202" s="11" t="n"/>
-      <c r="H202" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I202" s="8" t="inlineStr">
+      <c r="F202" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G202" s="10" t="n"/>
+      <c r="H202" s="11" t="n"/>
+      <c r="I202" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J202" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4049,12 +5043,17 @@
       <c r="C203" s="9" t="n"/>
       <c r="D203" s="8" t="n"/>
       <c r="E203" s="8" t="n"/>
-      <c r="F203" s="10" t="n"/>
-      <c r="G203" s="11" t="n"/>
-      <c r="H203" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I203" s="8" t="inlineStr">
+      <c r="F203" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G203" s="10" t="n"/>
+      <c r="H203" s="11" t="n"/>
+      <c r="I203" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J203" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4066,12 +5065,17 @@
       <c r="C204" s="9" t="n"/>
       <c r="D204" s="8" t="n"/>
       <c r="E204" s="8" t="n"/>
-      <c r="F204" s="10" t="n"/>
-      <c r="G204" s="11" t="n"/>
-      <c r="H204" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I204" s="8" t="inlineStr">
+      <c r="F204" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G204" s="10" t="n"/>
+      <c r="H204" s="11" t="n"/>
+      <c r="I204" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J204" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4083,12 +5087,17 @@
       <c r="C205" s="9" t="n"/>
       <c r="D205" s="8" t="n"/>
       <c r="E205" s="8" t="n"/>
-      <c r="F205" s="10" t="n"/>
-      <c r="G205" s="11" t="n"/>
-      <c r="H205" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I205" s="8" t="inlineStr">
+      <c r="F205" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G205" s="10" t="n"/>
+      <c r="H205" s="11" t="n"/>
+      <c r="I205" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J205" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4100,12 +5109,17 @@
       <c r="C206" s="9" t="n"/>
       <c r="D206" s="8" t="n"/>
       <c r="E206" s="8" t="n"/>
-      <c r="F206" s="10" t="n"/>
-      <c r="G206" s="11" t="n"/>
-      <c r="H206" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I206" s="8" t="inlineStr">
+      <c r="F206" s="8" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G206" s="10" t="n"/>
+      <c r="H206" s="11" t="n"/>
+      <c r="I206" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J206" s="8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -4113,16 +5127,19 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="I7:I206" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Digite SIM ou NÃO" type="list">
+  <dataValidations count="3">
+    <dataValidation sqref="F7:F206" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Contrato inválido" error="Digite CLT ou PJ" type="list">
+      <formula1>"CLT,PJ"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J7:J206" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Digite SIM ou NÃO" type="list">
       <formula1>"SIM,NÃO"</formula1>
     </dataValidation>
-    <dataValidation sqref="H7:H206" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Horas inválidas" error="Entre 1 e 24" type="decimal" operator="between">
+    <dataValidation sqref="I7:I206" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="decimal" operator="between">
       <formula1>1</formula1>
       <formula2>24</formula2>
     </dataValidation>
@@ -4137,340 +5154,320 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="4" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>Cargos / Funções</t>
-        </is>
-      </c>
-      <c r="C1" s="12" t="inlineStr">
-        <is>
-          <t>Setores de Trabalho</t>
-        </is>
-      </c>
-      <c r="E1" s="12" t="inlineStr">
-        <is>
-          <t>Referência Salarial</t>
+          <t>Calculadora: Salário Mensal ↔ Custo por Hora  |  CLT (220h) vs PJ (176h)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
         <is>
+          <t>Cargo / Referência</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>CLT (220h) — Custo/h</t>
+        </is>
+      </c>
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>CLT — Mensal</t>
+        </is>
+      </c>
+      <c r="E2" s="15" t="inlineStr">
+        <is>
+          <t>PJ (176h) — Custo/h</t>
+        </is>
+      </c>
+      <c r="F2" s="15" t="inlineStr">
+        <is>
+          <t>PJ — Mensal</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
           <t>Auxiliar Elétrico</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
-        <is>
-          <t>R$ 1.760 – R$ 2.640/mês</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="B3" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" s="18" t="n">
+        <v>2200</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F3" s="18" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Eletricista de Instalação</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="C4" s="18" t="n">
+        <v>2860</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="F4" s="18" t="n">
+        <v>2860</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Eletricista Industrial</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
-        <is>
-          <t>R$ 2.640 – R$ 4.400/mês</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="B5" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C5" s="18" t="n">
+        <v>3520</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="F5" s="18" t="n">
+        <v>3520</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>Eletricista Sênior</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="C6" s="18" t="n">
+        <v>4400</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="F6" s="18" t="n">
+        <v>4400</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Técnico em Automação</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>R$ 3.300 – R$ 5.500/mês</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="B7" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="C7" s="18" t="n">
+        <v>4400</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>4400</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Técnico Sênior</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="C8" s="18" t="n">
+        <v>6600</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Programador CLP</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>R$ 5.500 – R$ 9.900/mês</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Engenheiro Eletricista</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>R$ 7.700 – R$ 15.400/mês</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>Engenheiro de Automação</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>R$ 8.800 – R$ 17.600/mês</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="B9" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>7700</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Eng. Eletricista Jr.</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="C10" s="18" t="n">
+        <v>8800</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>8800</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Eng. Eletricista Pleno</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="C11" s="18" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Eng. Eletricista Sênior</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>15400</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>15400</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Supervisor de Obras</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>R$ 5.500 – R$ 9.900/mês</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
-        <is>
-          <t>Conversor: Salário Mensal → Custo por Hora</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="13" t="inlineStr"/>
-      <c r="B2" s="16" t="inlineStr">
-        <is>
-          <t>Salário Mensal</t>
-        </is>
-      </c>
-      <c r="C2" s="17" t="inlineStr">
-        <is>
-          <t>Custo/Hora (÷220)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="18" t="inlineStr">
-        <is>
-          <t>Auxiliar Elétrico</t>
-        </is>
-      </c>
-      <c r="B3" s="19" t="inlineStr">
-        <is>
-          <t>R$ 2.200,00</t>
-        </is>
-      </c>
-      <c r="C3" s="20">
-        <f>B3/220</f>
+      <c r="B13" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>7700</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>Gerente de Projetos</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>13200</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>75</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>13200</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr"/>
+      <c r="B15" s="17">
+        <f>C15/220</f>
         <v/>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>Eletricista Industrial</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>R$ 3.520,00</t>
-        </is>
-      </c>
-      <c r="C4" s="17">
-        <f>B4/220</f>
+      <c r="C15" s="19" t="n">
+        <v>13200</v>
+      </c>
+      <c r="E15" s="17">
+        <f>F15/176</f>
         <v/>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>Eletricista Sênior</t>
-        </is>
-      </c>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t>R$ 4.400,00</t>
-        </is>
-      </c>
-      <c r="C5" s="22">
-        <f>B5/220</f>
+      <c r="F15" s="19" t="n">
+        <v>13200</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>✏️ Informe seu salário →</t>
+        </is>
+      </c>
+      <c r="B16" s="17">
+        <f>C16/220</f>
         <v/>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Técnico em Automação</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>R$ 4.400,00</t>
-        </is>
-      </c>
-      <c r="C6" s="17">
-        <f>B6/220</f>
+      <c r="C16" s="19" t="n">
+        <v>13200</v>
+      </c>
+      <c r="E16" s="17">
+        <f>F16/176</f>
         <v/>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>Técnico Sênior</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>R$ 6.600,00</t>
-        </is>
-      </c>
-      <c r="C7" s="22">
-        <f>B7/220</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>Programador CLP</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>R$ 7.700,00</t>
-        </is>
-      </c>
-      <c r="C8" s="17">
-        <f>B8/220</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>Engenheiro Jr.</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t>R$ 8.800,00</t>
-        </is>
-      </c>
-      <c r="C9" s="22">
-        <f>B9/220</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>Engenheiro Pleno</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>R$ 11.000,00</t>
-        </is>
-      </c>
-      <c r="C10" s="17">
-        <f>B10/220</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>Engenheiro Sênior</t>
-        </is>
-      </c>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t>R$ 15.400,00</t>
-        </is>
-      </c>
-      <c r="C11" s="22">
-        <f>B11/220</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>Supervisor</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>R$ 7.700,00</t>
-        </is>
-      </c>
-      <c r="C12" s="17">
-        <f>B12/220</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr"/>
-      <c r="B13" s="21" t="inlineStr"/>
-      <c r="C13" s="22" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>✏️  Informe qualquer salário →</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="C14" s="17">
-        <f>B14/220</f>
-        <v/>
+      <c r="F16" s="19" t="n">
+        <v>13200</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
